--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.1%</t>
+          <t>449.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-663.8%</t>
+          <t>-641.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-159.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.6%</t>
+          <t>-250.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.4%</t>
+          <t>-163.5%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>3.030142637716717</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.841188244964981</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7951191162272571</v>
+        <v>1.093310915416978</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.71922352489871</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>3.100432870038893</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.781297563322387</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8893656212064696</v>
+        <v>1.18755742039619</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.825448166206441</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>3.115060606154936</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.879038107947362</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8648971394725236</v>
+        <v>1.163088938662244</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.830542335442697</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>3.113596586979608</v>
       </c>
       <c r="D1974" t="n">
         <v>-5.055375868070291</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7928980162480235</v>
+        <v>1.091089815437744</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.723275660193611</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>3.112088205019536</v>
       </c>
       <c r="D1975" t="n">
         <v>-5.054686495909068</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7916653831524414</v>
+        <v>1.089857182342162</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.721767278233539</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>3.111951072454973</v>
       </c>
       <c r="D1976" t="n">
         <v>-5.06125746096366</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7888998645660403</v>
+        <v>1.087091663755761</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.717687566636219</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>3.111951072454973</v>
       </c>
       <c r="D1977" t="n">
         <v>-5.053303490668888</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7920814526839495</v>
+        <v>1.09027325187367</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.717687566636219</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>3.118332829482777</v>
       </c>
       <c r="D1978" t="n">
         <v>-5.042930114335801</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8026125602449885</v>
+        <v>1.100804359434709</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.730293349463877</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>3.123225202857502</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.915245804541505</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8585786575374321</v>
+        <v>1.156770456727153</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.811796308715179</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>3.109979875333374</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.975912394943894</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8210666938523488</v>
+        <v>1.119258493042069</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.749531991159932</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>3.114077577944003</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.910918535010248</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8511619404364357</v>
+        <v>1.149353739626156</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.769728062533053</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>3.118238517575081</v>
       </c>
       <c r="D1982" t="n">
         <v>-5.011677170767246</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8150194257647145</v>
+        <v>1.113211224954435</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.720593660927928</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.124118120102918</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.967474333681346</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8385801631269116</v>
+        <v>1.136771962316632</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.752994965707305</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>3.122528120572166</v>
       </c>
       <c r="D1984" t="n">
         <v>-5.004453361344789</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8221985525307822</v>
+        <v>1.120390351720503</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.475397508061631</v>
+        <v>2.773589307251351</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.871138779544149</v>
+        <v>3.415949682270783</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.173775885755205</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.02183563798674</v>
+        <v>-4.799566726528115</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8664934070570411</v>
+        <v>1.253592770830212</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.52664527324467</v>
+        <v>2.824837072434391</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>-24.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-686.2%</t>
+          <t>-681.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.3%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-641.5%</t>
+          <t>-659.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.9%</t>
+          <t>-273.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.0%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.1%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-159.3%</t>
+          <t>1488.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-250.9%</t>
+          <t>-287.8%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.5%</t>
+          <t>-193.4%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.726279334034179</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.647222379824827</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.069962107260841</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.511518393988778</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.276473884147863</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.425019741890228</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.580013160488028</v>
+        <v>-4.532314969926555</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.305376958054421</v>
+        <v>1.32445623427901</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.011818953637816</v>
+        <v>-4.964120763076343</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.11898752826191</v>
+        <v>1.138066804486499</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.246512947770368</v>
+        <v>-5.198814757208895</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.01339470561098</v>
+        <v>1.032473981835569</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.582175595000821</v>
+        <v>-5.534477404439348</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8777102383747644</v>
+        <v>0.8967895145993534</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.945801839901134</v>
+        <v>-5.898103649339661</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7387473006488805</v>
+        <v>0.7578265768734695</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.310929222539881</v>
+        <v>-6.263231031978408</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5919508625992131</v>
+        <v>0.6110301388238022</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.719517999720559</v>
+        <v>-6.671819809159086</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4272768957417008</v>
+        <v>0.4463561719662898</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.996094100036391</v>
+        <v>-6.948395909474918</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3118318880868287</v>
+        <v>0.3309111643114178</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.412485974323388</v>
+        <v>-7.364787783761916</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.143269188980907</v>
+        <v>0.1623484652054961</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.729097916864037</v>
+        <v>-7.681399726302564</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.02688310263332649</v>
+        <v>0.04596237885791599</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.074972738848846</v>
+        <v>-8.027274548287373</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1153672610149017</v>
+        <v>-0.09628798479031264</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.23855261703323</v>
+        <v>-8.190854426471757</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1823942922336546</v>
+        <v>-0.1633150160090655</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.535213958843428</v>
+        <v>-8.487515768281956</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2972798530285257</v>
+        <v>-0.2782005768039366</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.740245139617745</v>
+        <v>-8.692546949056272</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3833186298726554</v>
+        <v>-0.3642393536480664</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.123246528360376</v>
+        <v>-9.075548337798903</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5366212866912918</v>
+        <v>-0.5175420104667028</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.305116319345411</v>
+        <v>-9.257418128783938</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6067976871138758</v>
+        <v>-0.5877184108892863</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.664646641849412</v>
+        <v>-9.616948451287939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7452595128174262</v>
+        <v>-0.7261802365928371</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714995705303634</v>
+        <v>-9.667297514742161</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7574831182419373</v>
+        <v>-0.7384038420173482</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.81261498272503</v>
+        <v>-9.764916792163557</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7934890785887272</v>
+        <v>-0.7744098023641377</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.960141070730673</v>
+        <v>-9.9124428801692</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8496059574694121</v>
+        <v>-0.8305266812448227</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16439924606054</v>
+        <v>-10.11670105549906</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9257960304827151</v>
+        <v>-0.9067167542581256</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30620902026732</v>
+        <v>-10.25851082970585</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9780373856809939</v>
+        <v>-0.9589581094564052</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23273918859988</v>
+        <v>-10.1850409980384</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9332777515205937</v>
+        <v>-0.9141984752960042</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40786360598642</v>
+        <v>-10.36016541542495</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.988772297727694</v>
+        <v>-0.9696930215031045</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.64231570000091</v>
+        <v>-10.59461750943944</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089772300235086</v>
+        <v>-1.070693024010497</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.93011954453815</v>
+        <v>-10.88242135397667</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211566028823957</v>
+        <v>-1.192486752599369</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98290570013847</v>
+        <v>-10.935207509577</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231564701225532</v>
+        <v>-1.212485425000943</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10894249350676</v>
+        <v>-11.06124430294529</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.279285689943733</v>
+        <v>-1.260206413719144</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05692697953795</v>
+        <v>-11.00922878897648</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254489148669807</v>
+        <v>-1.235409872445218</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19859882126207</v>
+        <v>-11.1509006307006</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312633112258196</v>
+        <v>-1.293553836033608</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14900797683724</v>
+        <v>-11.10130978627576</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277743364323391</v>
+        <v>-1.258664088098801</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13620058383246</v>
+        <v>-11.08850239327099</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285671540768164</v>
+        <v>-1.266592264543575</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91035543111305</v>
+        <v>-10.86265724055158</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185754406644191</v>
+        <v>-1.166675130419601</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78577677477546</v>
+        <v>-10.73807858421399</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134783799553095</v>
+        <v>-1.115704523328505</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83867206281974</v>
+        <v>-10.79097387225827</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153308140608702</v>
+        <v>-1.134228864384113</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.554763331891</v>
+        <v>-10.50706514132952</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.034010943998566</v>
+        <v>-1.014931667773976</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48339693928135</v>
+        <v>-10.43569874871988</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.015201649348572</v>
+        <v>-0.996122373123983</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21956007207728</v>
+        <v>-10.17186188151581</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.919550383779852</v>
+        <v>-0.9004711075552625</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.952318271208881</v>
+        <v>-9.904620080647408</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8144882239318663</v>
+        <v>-0.7954089477072772</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.85441123253239</v>
+        <v>-9.806713041970918</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.775625723434731</v>
+        <v>-0.756546447210142</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.830457691556433</v>
+        <v>-9.78275950099496</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.765375800898854</v>
+        <v>-0.746296524674265</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.566397753233636</v>
+        <v>-9.518699562672163</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6730121417314878</v>
+        <v>-0.6539328655068983</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.859318129728798</v>
+        <v>-8.811619939167326</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3929673259898534</v>
+        <v>-0.3738880497652644</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.819133831362608</v>
+        <v>-8.771435640801135</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3765499827555359</v>
+        <v>-0.3574707065309468</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.739064035824804</v>
+        <v>-8.691365845263331</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3451552433196574</v>
+        <v>-0.3260759670950684</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505582813595204</v>
+        <v>-8.457884623033731</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.243838325589965</v>
+        <v>-0.2247590493653759</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.35591642258769</v>
+        <v>-8.308218232026217</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1868639794999187</v>
+        <v>-0.1677847032753297</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223640948956803</v>
+        <v>-8.17594275839533</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1385863033005368</v>
+        <v>-0.1195070270759477</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.033041274283649</v>
+        <v>-7.985343083722177</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0595313727436384</v>
+        <v>-0.0404520965190498</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.784041475600068</v>
+        <v>-7.736343285038596</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0529748879534524</v>
+        <v>0.07205416417804145</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889631465373173</v>
+        <v>-7.841933274811701</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1172370375550078</v>
+        <v>-0.0981577613304192</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-7.860668176930298</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.05710738030077156</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76042632608417</v>
+        <v>-7.712728135522698</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.136889562650488</v>
+        <v>-0.1178102864258994</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.743268175952876</v>
+        <v>-7.695569985391404</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1387402888514488</v>
+        <v>-0.1196610126268598</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699719769182185</v>
+        <v>-7.652021578620714</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1282815382382658</v>
+        <v>-0.1092022620136768</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457571375728327</v>
+        <v>-7.409873185166855</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01695982647557948</v>
+        <v>0.002119449749009572</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349312238605806</v>
+        <v>-7.301614048044334</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02087594883262422</v>
+        <v>0.03995522505721327</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.226021103788675</v>
+        <v>-7.178322913227203</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06769049677005379</v>
+        <v>0.08676977299464239</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204871904885231</v>
+        <v>-7.157173714323759</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08385115456875614</v>
+        <v>0.1029304307933447</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.961106462901787</v>
+        <v>-6.913408272340315</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1771380397091846</v>
+        <v>0.1962173159337732</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859343642624492</v>
+        <v>-6.81164545206302</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2199674817401185</v>
+        <v>0.2390467579647071</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.609493248675418</v>
+        <v>-6.561795058113946</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3126497143034506</v>
+        <v>0.3317289905280392</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433601156207985</v>
+        <v>-6.385902965646514</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3866056748110722</v>
+        <v>0.4056849510356608</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.262154693185521</v>
+        <v>-6.21445650262405</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4685117660746116</v>
+        <v>0.4875910422991998</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.037121693516698</v>
+        <v>-5.989423502955227</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5575454435584377</v>
+        <v>0.5766247197830263</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973485951282764</v>
+        <v>-5.925787760721293</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5876945415063286</v>
+        <v>0.6067738177309172</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880485910076866</v>
+        <v>-5.832787719515395</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6060888167724836</v>
+        <v>0.6251680929970722</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.640055413272005</v>
+        <v>-5.592357222710534</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7040040921193054</v>
+        <v>0.7230833683438935</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567812845100811</v>
+        <v>-5.52011465453934</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7368304332226034</v>
+        <v>0.7559097094471916</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514814522819423</v>
+        <v>-5.467116332257952</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7587083460524986</v>
+        <v>0.7777876222770868</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406009637339696</v>
+        <v>-5.358311446778225</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7992283714643826</v>
+        <v>0.8183076476889712</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185988839302685</v>
+        <v>-5.138290648741214</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.888815727689801</v>
+        <v>0.9078950039143896</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.053121150239408</v>
+        <v>-5.005422959677936</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9578569861169353</v>
+        <v>0.9769362623415239</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.893606046720038</v>
+        <v>-4.845907856158567</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.022808871964985</v>
+        <v>1.041888148189574</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7489339016203</v>
+        <v>-4.701235711058829</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09076583256632</v>
+        <v>1.109845108790908</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808808728977993</v>
+        <v>-4.761110538416522</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.052853393024669</v>
+        <v>1.071932669249257</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.722009231198983</v>
+        <v>-4.674311040637512</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.109973685458839</v>
+        <v>1.129052961683427</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724478937660789</v>
+        <v>-4.676780747099318</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.109058204247529</v>
+        <v>1.128137480472117</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7928491239848</v>
+        <v>-4.745150933423329</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.092717052192626</v>
+        <v>1.111796328417215</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.901387304900934</v>
+        <v>-4.853689114339462</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.039738488458064</v>
+        <v>1.058817764682653</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.932380464229639</v>
+        <v>-4.884682273668168</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8520507897669689</v>
+        <v>0.8711300659915573</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.75690620443717</v>
+        <v>-4.709208013875699</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9268077256757441</v>
+        <v>0.9458870019003325</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.867842457078419</v>
+        <v>-4.820144266516948</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8581752533804516</v>
+        <v>0.87725452960504</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.070869034621652</v>
+        <v>-5.023170844060181</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7800960075830639</v>
+        <v>0.7991752838076525</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.912943435686359</v>
+        <v>-4.865245245124888</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8534386335893134</v>
+        <v>0.8725179098139018</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.826699972659982</v>
+        <v>-4.77900178209851</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8828822893737249</v>
+        <v>0.9019615655983133</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.872006792058961</v>
+        <v>-4.82430860149749</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8565353370586584</v>
+        <v>0.875614613283247</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.901039896761263</v>
+        <v>-4.853341706199791</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8454739682108396</v>
+        <v>0.864553244435428</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.808229415310403</v>
+        <v>-4.760531224748932</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8118708526825491</v>
+        <v>0.8309501289071375</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.85261888463983</v>
+        <v>-4.804920694078359</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7959885408753788</v>
+        <v>0.8150678170999672</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.73994766640358</v>
+        <v>-4.692249475842109</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.836132736681602</v>
+        <v>0.8552120129061904</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.627570665220907</v>
+        <v>-4.579872474659436</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8865748329853385</v>
+        <v>0.9056541092099268</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.825805234107638</v>
+        <v>-4.778107043546167</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8187782071991851</v>
+        <v>0.8378574834237735</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.908806515132917</v>
+        <v>-4.861108324571446</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6239334147897269</v>
+        <v>0.6430126910143152</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.017420593576248</v>
+        <v>-4.969722403014777</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7006374441315999</v>
+        <v>0.7197167203561885</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.104019176557351</v>
+        <v>-5.05632098599588</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.680511037041482</v>
+        <v>0.6995903132660701</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.0656355139992</v>
+        <v>-5.017937323437729</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6932839434071107</v>
+        <v>0.7123632196316994</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.888519183964034</v>
+        <v>-4.840820993402563</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7608595042664792</v>
+        <v>0.7799387804910678</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.85881705998774</v>
+        <v>-4.811118869426269</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7734237456189099</v>
+        <v>0.7925030218434983</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.679441638748973</v>
+        <v>-4.631743448187501</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8389608894208314</v>
+        <v>0.8580401656454197</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.724455852269578</v>
+        <v>-4.676757661708107</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8017626593441787</v>
+        <v>0.8208419355687671</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.991460362542013</v>
+        <v>-4.943762171980542</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7006524175741504</v>
+        <v>0.7197316937987388</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.092658143979186</v>
+        <v>-5.044959953417715</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6593772268957827</v>
+        <v>0.6784565031203713</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.060182557808414</v>
+        <v>-5.012484367246943</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6699674229184085</v>
+        <v>0.6890466991429967</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.041144430101117</v>
+        <v>-4.993446239539646</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6741073932095722</v>
+        <v>0.6931866694341606</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.072271061251735</v>
+        <v>-5.024572870690264</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8392386096880053</v>
+        <v>0.8583178859125939</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.124591441852527</v>
+        <v>-5.076893251291056</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8191437864338225</v>
+        <v>0.8382230626584106</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.144848740381485</v>
+        <v>-5.097150549820014</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.817049397419165</v>
+        <v>0.8361286736437537</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.997105770146482</v>
+        <v>-4.949407579585011</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.955299233305188</v>
+        <v>0.9743785095297763</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.099120452677703</v>
+        <v>-5.051422262116232</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9172869818241804</v>
+        <v>0.9363662580487691</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.962511108583611</v>
+        <v>-4.91481291802214</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.972593067853476</v>
+        <v>0.9916723440780644</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.105276441406261</v>
+        <v>-5.05757825084479</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9145674114645259</v>
+        <v>0.9336466876891145</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.042978442630139</v>
+        <v>-4.995280252068667</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.005822164771796</v>
+        <v>1.024901440996384</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.030142637716717</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.841188244964981</v>
+        <v>-4.79349005440351</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.093310915416978</v>
+        <v>0.8141983924518454</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.71922352489871</v>
+        <v>2.421031725708989</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.100432870038893</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.781297563322387</v>
+        <v>-4.733599372760916</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.18755742039619</v>
+        <v>0.9084448974310582</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.825448166206441</v>
+        <v>2.527256367016721</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.115060606154936</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.879038107947362</v>
+        <v>-4.831339917385891</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.163088938662244</v>
+        <v>0.8839764156971119</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.830542335442697</v>
+        <v>2.532350536252976</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.113596586979608</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.055375868070291</v>
+        <v>-5.00767767750882</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.091089815437744</v>
+        <v>0.8119772924726119</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.723275660193611</v>
+        <v>2.42508386100389</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.112088205019536</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.054686495909068</v>
+        <v>-5.006988305347597</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.089857182342162</v>
+        <v>0.8107446593770298</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.721767278233539</v>
+        <v>2.423575479043818</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.111951072454973</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.06125746096366</v>
+        <v>-5.013559270402189</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.087091663755761</v>
+        <v>0.8079791407906289</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717687566636219</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.111951072454973</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.053303490668888</v>
+        <v>-5.005605300107417</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.09027325187367</v>
+        <v>0.8111607289085376</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717687566636219</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.118332829482777</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.042930114335801</v>
+        <v>-4.99523192377433</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.100804359434709</v>
+        <v>0.8216918364695771</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.730293349463877</v>
+        <v>2.432101550274156</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.123225202857502</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.915245804541505</v>
+        <v>-4.867547613980034</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.156770456727153</v>
+        <v>0.8776579337620205</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.811796308715179</v>
+        <v>2.513604509525459</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.109979875333374</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.975912394943894</v>
+        <v>-4.928214204382423</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.119258493042069</v>
+        <v>0.8401459700769371</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.749531991159932</v>
+        <v>2.451340191970211</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.114077577944003</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.910918535010248</v>
+        <v>-4.863220344448777</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.149353739626156</v>
+        <v>0.8702412166610241</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.769728062533053</v>
+        <v>2.471536263343332</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.118238517575081</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.011677170767246</v>
+        <v>-4.963978980205775</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.113211224954435</v>
+        <v>0.8340987019893027</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.720593660927928</v>
+        <v>2.422401861738207</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.124118120102918</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.967474333681346</v>
+        <v>-4.919776143119875</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.136771962316632</v>
+        <v>0.8576594393515</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.752994965707305</v>
+        <v>2.454803166517585</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.122528120572166</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.004453361344789</v>
+        <v>-4.956755170783318</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.120390351720503</v>
+        <v>0.8412778287553706</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.773589307251351</v>
+        <v>2.475397508061631</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.415949682270783</v>
+        <v>3.819004927721788</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.173775885755205</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.799566726528115</v>
+        <v>-4.976813249648158</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.253592770830212</v>
+        <v>0.8845023623924739</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.824837072434391</v>
+        <v>2.52664527324467</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-12.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.5%</t>
+          <t>-686.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.3%</t>
+          <t>-664.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.0%</t>
+          <t>-274.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1488.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.8%</t>
+          <t>-277.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-193.4%</t>
+          <t>-181.4%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.726279334034179</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.647222379824827</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.069962107260841</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.511518393988778</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.276473884147863</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.425019741890228</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.532314969926555</v>
+        <v>-4.580013160488028</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.32445623427901</v>
+        <v>1.305376958054421</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.964120763076343</v>
+        <v>-5.011818953637816</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.138066804486499</v>
+        <v>1.11898752826191</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.198814757208895</v>
+        <v>-5.246512947770368</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.032473981835569</v>
+        <v>1.01339470561098</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.534477404439348</v>
+        <v>-5.582175595000821</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8967895145993534</v>
+        <v>0.8777102383747644</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.898103649339661</v>
+        <v>-5.945801839901134</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7578265768734695</v>
+        <v>0.7387473006488805</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.263231031978408</v>
+        <v>-6.310929222539881</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6110301388238022</v>
+        <v>0.5919508625992131</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.671819809159086</v>
+        <v>-6.719517999720559</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4463561719662898</v>
+        <v>0.4272768957417008</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.948395909474918</v>
+        <v>-6.996094100036391</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3309111643114178</v>
+        <v>0.3118318880868287</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.364787783761916</v>
+        <v>-7.412485974323388</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1623484652054961</v>
+        <v>0.143269188980907</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.681399726302564</v>
+        <v>-7.729097916864037</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04596237885791599</v>
+        <v>0.02688310263332649</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.027274548287373</v>
+        <v>-8.074972738848846</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09628798479031264</v>
+        <v>-0.1153672610149017</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.190854426471757</v>
+        <v>-8.23855261703323</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1633150160090655</v>
+        <v>-0.1823942922336546</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.487515768281956</v>
+        <v>-8.535213958843428</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2782005768039366</v>
+        <v>-0.2972798530285257</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.692546949056272</v>
+        <v>-8.740245139617745</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3642393536480664</v>
+        <v>-0.3833186298726554</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.075548337798903</v>
+        <v>-9.123246528360376</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5175420104667028</v>
+        <v>-0.5366212866912918</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.257418128783938</v>
+        <v>-9.305116319345411</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5877184108892863</v>
+        <v>-0.6067976871138758</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.616948451287939</v>
+        <v>-9.664646641849412</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7261802365928371</v>
+        <v>-0.7452595128174262</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.667297514742161</v>
+        <v>-9.714995705303634</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7384038420173482</v>
+        <v>-0.7574831182419373</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.764916792163557</v>
+        <v>-9.81261498272503</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7744098023641377</v>
+        <v>-0.7934890785887272</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.9124428801692</v>
+        <v>-9.960141070730673</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8305266812448227</v>
+        <v>-0.8496059574694121</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.11670105549906</v>
+        <v>-10.16439924606054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9067167542581256</v>
+        <v>-0.9257960304827151</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.25851082970585</v>
+        <v>-10.30620902026732</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9589581094564052</v>
+        <v>-0.9780373856809939</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.1850409980384</v>
+        <v>-10.23273918859988</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9141984752960042</v>
+        <v>-0.9332777515205937</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.36016541542495</v>
+        <v>-10.40786360598642</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9696930215031045</v>
+        <v>-0.988772297727694</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.59461750943944</v>
+        <v>-10.64231570000091</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.070693024010497</v>
+        <v>-1.089772300235086</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.88242135397667</v>
+        <v>-10.93011954453815</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.192486752599369</v>
+        <v>-1.211566028823957</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.935207509577</v>
+        <v>-10.98290570013847</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.212485425000943</v>
+        <v>-1.231564701225532</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.06124430294529</v>
+        <v>-11.10894249350676</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.260206413719144</v>
+        <v>-1.279285689943733</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.00922878897648</v>
+        <v>-11.05692697953795</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.235409872445218</v>
+        <v>-1.254489148669807</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.1509006307006</v>
+        <v>-11.19859882126207</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.293553836033608</v>
+        <v>-1.312633112258196</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.10130978627576</v>
+        <v>-11.14900797683724</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.258664088098801</v>
+        <v>-1.277743364323391</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.08850239327099</v>
+        <v>-11.13620058383246</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.266592264543575</v>
+        <v>-1.285671540768164</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.86265724055158</v>
+        <v>-10.91035543111305</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.166675130419601</v>
+        <v>-1.185754406644191</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.73807858421399</v>
+        <v>-10.78577677477546</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.115704523328505</v>
+        <v>-1.134783799553095</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.79097387225827</v>
+        <v>-10.83867206281974</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.134228864384113</v>
+        <v>-1.153308140608702</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.50706514132952</v>
+        <v>-10.554763331891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.014931667773976</v>
+        <v>-1.034010943998566</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.43569874871988</v>
+        <v>-10.48339693928135</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.996122373123983</v>
+        <v>-1.015201649348572</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17186188151581</v>
+        <v>-10.21956007207728</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9004711075552625</v>
+        <v>-0.919550383779852</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.904620080647408</v>
+        <v>-9.952318271208881</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7954089477072772</v>
+        <v>-0.8144882239318663</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.806713041970918</v>
+        <v>-9.85441123253239</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.756546447210142</v>
+        <v>-0.775625723434731</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.78275950099496</v>
+        <v>-9.830457691556433</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.746296524674265</v>
+        <v>-0.765375800898854</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.518699562672163</v>
+        <v>-9.566397753233636</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6539328655068983</v>
+        <v>-0.6730121417314878</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.811619939167326</v>
+        <v>-8.859318129728798</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3738880497652644</v>
+        <v>-0.3929673259898534</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.771435640801135</v>
+        <v>-8.819133831362608</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3574707065309468</v>
+        <v>-0.3765499827555359</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.691365845263331</v>
+        <v>-8.739064035824804</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3260759670950684</v>
+        <v>-0.3451552433196574</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.457884623033731</v>
+        <v>-8.505582813595204</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2247590493653759</v>
+        <v>-0.243838325589965</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.308218232026217</v>
+        <v>-8.35591642258769</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1677847032753297</v>
+        <v>-0.1868639794999187</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.17594275839533</v>
+        <v>-8.223640948956803</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1195070270759477</v>
+        <v>-0.1385863033005368</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.985343083722177</v>
+        <v>-8.033041274283649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0404520965190498</v>
+        <v>-0.0595313727436384</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.736343285038596</v>
+        <v>-7.784041475600068</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07205416417804145</v>
+        <v>0.0529748879534524</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.841933274811701</v>
+        <v>-7.889631465373173</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.0981577613304192</v>
+        <v>-0.1172370375550078</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.860668176930298</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05710738030077156</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.087258864897787</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.712728135522698</v>
+        <v>-7.76042632608417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1178102864258994</v>
+        <v>-0.01726808984962869</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.902224179537755</v>
+        <v>2.021845652338614</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.078544878644308</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.695569985391404</v>
+        <v>-7.743268175952876</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1196610126268598</v>
+        <v>-0.01911881605058952</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.903805083363053</v>
+        <v>2.023426556163912</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.071584266549215</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.652021578620714</v>
+        <v>-7.699719769182185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1092022620136768</v>
+        <v>-0.008660065437406494</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.89684447126796</v>
+        <v>2.016465944068819</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.086046620930358</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.409873185166855</v>
+        <v>-7.457571375728327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.002119449749009572</v>
+        <v>0.1026616463252799</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.911306825649103</v>
+        <v>2.030928298449962</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.080578741389553</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.301614048044334</v>
+        <v>-7.349312238605806</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03995522505721327</v>
+        <v>0.1404974216334836</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.905838946108298</v>
+        <v>2.025460418909157</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.07807683540013</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.178322913227203</v>
+        <v>-7.226021103788675</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08676977299464239</v>
+        <v>0.1873119695709131</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.977311721009153</v>
+        <v>2.096933193810012</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.085777813637455</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.157173714323759</v>
+        <v>-7.204871904885231</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1029304307933447</v>
+        <v>0.2034726273696155</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.997702218588544</v>
+        <v>2.117323691389403</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.081558521984506</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.913408272340315</v>
+        <v>-6.961106462901787</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1962173159337732</v>
+        <v>0.296759512510044</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.993482926935595</v>
+        <v>2.113104399736454</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.083682835904522</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.81164545206302</v>
+        <v>-6.859343642624492</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2390467579647071</v>
+        <v>0.3395889545409778</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.003538681891068</v>
+        <v>2.123160154691927</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.076424910888224</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.561795058113946</v>
+        <v>-6.609493248675418</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3317289905280392</v>
+        <v>0.4322711871043099</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.99628075687477</v>
+        <v>2.11590222967563</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.080024034408873</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.385902965646514</v>
+        <v>-6.433601156207985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4056849510356608</v>
+        <v>0.5062271476119315</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.999879880395419</v>
+        <v>2.119501353196278</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.093351540463427</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.21445650262405</v>
+        <v>-6.262154693185521</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4875910422991998</v>
+        <v>0.588133238875471</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116075264263451</v>
+        <v>2.23569673706431</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.092372018079724</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.989423502955227</v>
+        <v>-6.037121693516698</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5766247197830263</v>
+        <v>0.677166916359297</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.250115541681041</v>
+        <v>2.369737014481901</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.097066819134041</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.925787760721293</v>
+        <v>-5.973485951282764</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6067738177309172</v>
+        <v>0.7073160143071879</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.292991788075719</v>
+        <v>2.412613260876578</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.078261077917837</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.832787719515395</v>
+        <v>-5.880485910076866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6251680929970722</v>
+        <v>0.7257102895733429</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.274186046859515</v>
+        <v>2.393807519660374</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.080004154542714</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.592357222710534</v>
+        <v>-5.640055413272005</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7230833683438935</v>
+        <v>0.8236255649201647</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.420187421567308</v>
+        <v>2.539808894368168</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.083933468377534</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.52011465453934</v>
+        <v>-5.567812845100811</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7559097094471916</v>
+        <v>0.8564519060234628</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.424116735402129</v>
+        <v>2.543738208202988</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.084612052294874</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.467116332257952</v>
+        <v>-5.514814522819423</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7777876222770868</v>
+        <v>0.8783298188533579</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.457997074720632</v>
+        <v>2.577618547521491</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.081610123514868</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.358311446778225</v>
+        <v>-5.406009637339696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8183076476889712</v>
+        <v>0.918849844265242</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.454995145940625</v>
+        <v>2.574616618741485</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.083189160525482</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.138290648741214</v>
+        <v>-5.185988839302685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9078950039143896</v>
+        <v>1.00843720049066</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.541306089992028</v>
+        <v>2.660927562792887</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.099083343327305</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.005422959677936</v>
+        <v>-5.053121150239408</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9769362623415239</v>
+        <v>1.077478458917795</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.557200272793851</v>
+        <v>2.67682174559471</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.100229187767607</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.845907856158567</v>
+        <v>-4.893606046720038</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.041888148189574</v>
+        <v>1.142430344765845</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.654055179345775</v>
+        <v>2.773676652146634</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.110317290329047</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.701235711058829</v>
+        <v>-4.7489339016203</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.109845108790908</v>
+        <v>1.210387305367179</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.750946568967057</v>
+        <v>2.870568041767917</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.096354781730473</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.761110538416522</v>
+        <v>-4.808808728977993</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.071932669249257</v>
+        <v>1.172474865825528</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.701059163953868</v>
+        <v>2.820680636754727</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.118755275053039</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.674311040637512</v>
+        <v>-4.722009231198983</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.129052961683427</v>
+        <v>1.229595158259698</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.723459657276434</v>
+        <v>2.843081130077293</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.118827676426451</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.676780747099318</v>
+        <v>-4.724478937660789</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.128137480472117</v>
+        <v>1.228679677048388</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.722050234772762</v>
+        <v>2.841671707573622</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.129834598901153</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.745150933423329</v>
+        <v>-4.7928491239848</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.111796328417215</v>
+        <v>1.212338524993486</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.738622576669193</v>
+        <v>2.858244049470053</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.120271307533044</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.853689114339462</v>
+        <v>-4.901387304900934</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.058817764682653</v>
+        <v>1.159359961258923</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.729059285301084</v>
+        <v>2.848680758101944</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.944980872573431</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.884682273668168</v>
+        <v>-4.932380464229639</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8711300659915573</v>
+        <v>0.9716722625678282</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.553768850341471</v>
+        <v>2.673390323142331</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.949548104565219</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.709208013875699</v>
+        <v>-4.75690620443717</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9458870019003325</v>
+        <v>1.046429198476603</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.558336082333259</v>
+        <v>2.677957555134118</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.925290133326426</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.820144266516948</v>
+        <v>-4.867842457078419</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.87725452960504</v>
+        <v>0.977796726181311</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.534078111094466</v>
+        <v>2.653699583895325</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.928421518546331</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.023170844060181</v>
+        <v>-5.070869034621652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7991752838076525</v>
+        <v>0.8997174803839232</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.415393549788432</v>
+        <v>2.535015022589291</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.938593904978464</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.865245245124888</v>
+        <v>-4.912943435686359</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8725179098139018</v>
+        <v>0.9730601063901727</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.425565936220564</v>
+        <v>2.545187409021423</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.933540175552324</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.77900178209851</v>
+        <v>-4.826699972659982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9019615655983133</v>
+        <v>1.002503762174584</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.420512206794424</v>
+        <v>2.540133679595284</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.92531595099685</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.82430860149749</v>
+        <v>-4.872006792058961</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.875614613283247</v>
+        <v>0.9761568098595177</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.387801884433411</v>
+        <v>2.507423357234271</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.925867824029951</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.853341706199791</v>
+        <v>-4.901039896761263</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.864553244435428</v>
+        <v>0.965095441011699</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.388353757466513</v>
+        <v>2.507975230267372</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.855140515921317</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.760531224748932</v>
+        <v>-4.808229415310403</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8309501289071375</v>
+        <v>0.9314923254834084</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.373312738228394</v>
+        <v>2.492934211029254</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.857013991845918</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.804920694078359</v>
+        <v>-4.85261888463983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8150678170999672</v>
+        <v>0.9156100136762382</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.348552532555338</v>
+        <v>2.468174005356198</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.852089700357641</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.692249475842109</v>
+        <v>-4.73994766640358</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8552120129061904</v>
+        <v>0.9557542094824614</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.411230972008811</v>
+        <v>2.530852444809671</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.857580996188308</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.579872474659436</v>
+        <v>-4.627570665220907</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9056541092099268</v>
+        <v>1.006196305786198</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.416722267839479</v>
+        <v>2.536343740640338</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.869078197956847</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.778107043546167</v>
+        <v>-4.825805234107638</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8378574834237735</v>
+        <v>0.9383996800000445</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.309278728275979</v>
+        <v>2.428900201076839</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.7074339179575</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.861108324571446</v>
+        <v>-4.908806515132917</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6430126910143152</v>
+        <v>0.7435548875905862</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.136491917560329</v>
+        <v>2.256113390361188</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.827583578676706</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.969722403014777</v>
+        <v>-5.017420593576248</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7197167203561885</v>
+        <v>0.8202589169324592</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.256641578279534</v>
+        <v>2.376263051080393</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.842096604779029</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.05632098599588</v>
+        <v>-5.104019176557351</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6995903132660701</v>
+        <v>0.8001325098423413</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.271154604381857</v>
+        <v>2.390776077182716</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.839516046121398</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.017937323437729</v>
+        <v>-5.0656355139992</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7123632196316994</v>
+        <v>0.8129054162079701</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.291604243259116</v>
+        <v>2.411225716059976</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.836245074966699</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.840820993402563</v>
+        <v>-4.888519183964034</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7799387804910678</v>
+        <v>0.8804809770673385</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.288333272104418</v>
+        <v>2.407954744905278</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.836928466728613</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.811118869426269</v>
+        <v>-4.85881705998774</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7925030218434983</v>
+        <v>0.8930452184197692</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.286334588737144</v>
+        <v>2.405956061538003</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.830715442035027</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.631743448187501</v>
+        <v>-4.679441638748973</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8580401656454197</v>
+        <v>0.9585823622216907</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.374187618945989</v>
+        <v>2.493809091746849</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.811522897366617</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.676757661708107</v>
+        <v>-4.724455852269578</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8208419355687671</v>
+        <v>0.921384132145038</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.336785737088816</v>
+        <v>2.456407209889675</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.817214459705562</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.943762171980542</v>
+        <v>-4.991460362542013</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7197316937987388</v>
+        <v>0.8202738903750098</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.225859476601993</v>
+        <v>2.345480949402852</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.816418381602064</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.044959953417715</v>
+        <v>-5.092658143979186</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6784565031203713</v>
+        <v>0.778998699696642</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.184018110371303</v>
+        <v>2.303639583172162</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.814018343156381</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.012484367246943</v>
+        <v>-5.060182557808414</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6890466991429967</v>
+        <v>0.7895888957192678</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.18161807192562</v>
+        <v>2.301239544726479</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.810543062364625</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.993446239539646</v>
+        <v>-5.041144430101117</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6931866694341606</v>
+        <v>0.7937288660104316</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.143232624335147</v>
+        <v>2.262854097136007</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.988124931303306</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.024572870690264</v>
+        <v>-5.072271061251735</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8583178859125939</v>
+        <v>0.9588600824888647</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.320814493273828</v>
+        <v>2.440435966074688</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.98895826028944</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.076893251291056</v>
+        <v>-5.124591441852527</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8382230626584106</v>
+        <v>0.9387652592346818</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.342615938265285</v>
+        <v>2.462237411066144</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.994966790686366</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.097150549820014</v>
+        <v>-5.144848740381485</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8361286736437537</v>
+        <v>0.9366708702200244</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.348624468662211</v>
+        <v>2.46824594146307</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.074119438478387</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.949407579585011</v>
+        <v>-4.997105770146482</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9743785095297763</v>
+        <v>1.074920706106047</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.528461530795163</v>
+        <v>2.648083003596022</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.076913060009868</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.051422262116232</v>
+        <v>-5.099120452677703</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9363662580487691</v>
+        <v>1.03690845462504</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.531255152326644</v>
+        <v>2.650876625127503</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.077575408401527</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.91481291802214</v>
+        <v>-4.962511108583611</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9916723440780644</v>
+        <v>1.092214540654335</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.613883107174757</v>
+        <v>2.733504579975617</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.076655885141637</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.05757825084479</v>
+        <v>-5.105276441406261</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9336466876891145</v>
+        <v>1.034188884265385</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.527304384221277</v>
+        <v>2.646925857022137</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.142991438938458</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.995280252068667</v>
+        <v>-5.042978442630139</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.024901440996384</v>
+        <v>1.125443637572655</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.593639938018098</v>
+        <v>2.713261410818958</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.851572311327856</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.79349005440351</v>
+        <v>-4.841188244964981</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8141983924518454</v>
+        <v>0.9147405890281164</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.421031725708989</v>
+        <v>2.540653198509848</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.921862543650031</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.733599372760916</v>
+        <v>-4.781297563322387</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9084448974310582</v>
+        <v>1.008987094007329</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.527256367016721</v>
+        <v>2.64687783981758</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.936490279766075</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.831339917385891</v>
+        <v>-4.879038107947362</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8839764156971119</v>
+        <v>0.9845186122733829</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.532350536252976</v>
+        <v>2.651972009053835</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.935026260590746</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.00767767750882</v>
+        <v>-5.055375868070291</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8119772924726119</v>
+        <v>0.9125194890488828</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.42508386100389</v>
+        <v>2.544705333804749</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.933517878630675</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.006988305347597</v>
+        <v>-5.054686495909068</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8107446593770298</v>
+        <v>0.9112868559533007</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.423575479043818</v>
+        <v>2.543196951844678</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933380746066111</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.013559270402189</v>
+        <v>-5.06125746096366</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8079791407906289</v>
+        <v>0.9085213373668997</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.419495767446499</v>
+        <v>2.539117240247358</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.933380746066111</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.005605300107417</v>
+        <v>-5.053303490668888</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8111607289085376</v>
+        <v>0.9117029254848088</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.419495767446499</v>
+        <v>2.539117240247358</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.939762503093916</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.99523192377433</v>
+        <v>-5.042930114335801</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8216918364695771</v>
+        <v>0.9222340330458478</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.432101550274156</v>
+        <v>2.551723023075015</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.944654876468641</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.867547613980034</v>
+        <v>-4.915245804541505</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8776579337620205</v>
+        <v>0.9782001303382915</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.513604509525459</v>
+        <v>2.633225982326318</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.931409548944513</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.928214204382423</v>
+        <v>-4.975912394943894</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8401459700769371</v>
+        <v>0.9406881666532081</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.451340191970211</v>
+        <v>2.57096166477107</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.935507251555141</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.863220344448777</v>
+        <v>-4.910918535010248</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8702412166610241</v>
+        <v>0.970783413237295</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.471536263343332</v>
+        <v>2.591157736144192</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.939668191186219</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.963978980205775</v>
+        <v>-5.011677170767246</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8340987019893027</v>
+        <v>0.9346408985655739</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.422401861738207</v>
+        <v>2.542023334539067</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.945547793714057</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.919776143119875</v>
+        <v>-4.967474333681346</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8576594393515</v>
+        <v>0.958201635927771</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.454803166517585</v>
+        <v>2.574424639318444</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.943957794183304</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.956755170783318</v>
+        <v>-5.004453361344789</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8412778287553706</v>
+        <v>0.9418200253316416</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.475397508061631</v>
+        <v>2.59501898086249</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.819004927721788</v>
+        <v>3.760495499820589</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.995205559366344</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.976813249648158</v>
+        <v>-5.024511440209629</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8845023623924739</v>
+        <v>0.9850445589687449</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.52664527324467</v>
+        <v>2.64626674604553</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-686.2%</t>
+          <t>-682.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.0%</t>
+          <t>-659.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.9%</t>
+          <t>-273.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.7%</t>
+          <t>-245.5%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-128.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1985"/>
+  <dimension ref="A1:G1986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.732584176345583</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.644700442900265</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.076266949572246</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.508996457064216</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.282778726459267</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.422497804965666</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.580013160488028</v>
+        <v>-4.53861981223796</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.305376958054421</v>
+        <v>1.321934297354448</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.011818953637816</v>
+        <v>-4.970425605387748</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.11898752826191</v>
+        <v>1.135544867561938</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.246512947770368</v>
+        <v>-5.2051195995203</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.01339470561098</v>
+        <v>1.029952044911007</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.582175595000821</v>
+        <v>-5.540782246750752</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8777102383747644</v>
+        <v>0.8942675776747913</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.945801839901134</v>
+        <v>-5.904408491651066</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7387473006488805</v>
+        <v>0.7553046399489078</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.310929222539881</v>
+        <v>-6.269535874289812</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5919508625992131</v>
+        <v>0.6085082018992405</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.719517999720559</v>
+        <v>-6.67812465147049</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4272768957417008</v>
+        <v>0.4438342350417281</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.996094100036391</v>
+        <v>-6.954700751786323</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3118318880868287</v>
+        <v>0.3283892273868556</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.412485974323388</v>
+        <v>-7.37109262607332</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.143269188980907</v>
+        <v>0.1598265282809344</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.729097916864037</v>
+        <v>-7.687704568613968</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.02688310263332649</v>
+        <v>0.04344044193335383</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.074972738848846</v>
+        <v>-8.033579390598778</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1153672610149017</v>
+        <v>-0.09880992171487479</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.23855261703323</v>
+        <v>-8.197159268783162</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1823942922336546</v>
+        <v>-0.1658369529336272</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.535213958843428</v>
+        <v>-8.49382061059336</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2972798530285257</v>
+        <v>-0.2807225137284983</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.740245139617745</v>
+        <v>-8.698851791367677</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3833186298726554</v>
+        <v>-0.3667612905726281</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.123246528360376</v>
+        <v>-9.081853180110308</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5366212866912918</v>
+        <v>-0.5200639473912645</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.305116319345411</v>
+        <v>-9.263722971095342</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6067976871138758</v>
+        <v>-0.5902403478138485</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.664646641849412</v>
+        <v>-9.623253293599344</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7452595128174262</v>
+        <v>-0.7287021735173989</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714995705303634</v>
+        <v>-9.673602357053566</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7574831182419373</v>
+        <v>-0.7409257789419104</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.81261498272503</v>
+        <v>-9.771221634474962</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7934890785887272</v>
+        <v>-0.7769317392886999</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.960141070730673</v>
+        <v>-9.918747722480605</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8496059574694121</v>
+        <v>-0.8330486181693848</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16439924606054</v>
+        <v>-10.12300589781047</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9257960304827151</v>
+        <v>-0.9092386911826882</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30620902026732</v>
+        <v>-10.26481567201726</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9780373856809939</v>
+        <v>-0.961480046380967</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23273918859988</v>
+        <v>-10.19134584034981</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9332777515205937</v>
+        <v>-0.9167204122205659</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40786360598642</v>
+        <v>-10.36647025773635</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.988772297727694</v>
+        <v>-0.9722149584276671</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.64231570000091</v>
+        <v>-10.60092235175084</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089772300235086</v>
+        <v>-1.073214960935058</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.93011954453815</v>
+        <v>-10.88872619628808</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211566028823957</v>
+        <v>-1.19500868952393</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98290570013847</v>
+        <v>-10.94151235188841</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231564701225532</v>
+        <v>-1.215007361925505</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10894249350676</v>
+        <v>-11.0675491452567</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.279285689943733</v>
+        <v>-1.262728350643706</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05692697953795</v>
+        <v>-11.01553363128788</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254489148669807</v>
+        <v>-1.23793180936978</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19859882126207</v>
+        <v>-11.157205473012</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312633112258196</v>
+        <v>-1.29607577295817</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14900797683724</v>
+        <v>-11.10761462858717</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277743364323391</v>
+        <v>-1.261186025023364</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13620058383246</v>
+        <v>-11.09480723558239</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285671540768164</v>
+        <v>-1.269114201468137</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91035543111305</v>
+        <v>-10.86896208286298</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185754406644191</v>
+        <v>-1.169197067344163</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78577677477546</v>
+        <v>-10.74438342652539</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134783799553095</v>
+        <v>-1.118226460253068</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83867206281974</v>
+        <v>-10.79727871456968</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153308140608702</v>
+        <v>-1.136750801308675</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.554763331891</v>
+        <v>-10.51336998364093</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.034010943998566</v>
+        <v>-1.017453604698539</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48339693928135</v>
+        <v>-10.44200359103128</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.015201649348572</v>
+        <v>-0.9986443100485447</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21956007207728</v>
+        <v>-10.17816672382721</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.919550383779852</v>
+        <v>-0.9029930444798242</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.952318271208881</v>
+        <v>-9.910924922958813</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8144882239318663</v>
+        <v>-0.7979308846318394</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.85441123253239</v>
+        <v>-9.813017884282322</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.775625723434731</v>
+        <v>-0.7590683841347037</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.830457691556433</v>
+        <v>-9.789064343306364</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.765375800898854</v>
+        <v>-0.7488184615988271</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.566397753233636</v>
+        <v>-9.525004404983568</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6730121417314878</v>
+        <v>-0.6564548024314605</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.859318129728798</v>
+        <v>-8.81792478147873</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3929673259898534</v>
+        <v>-0.3764099866898265</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.819133831362608</v>
+        <v>-8.77774048311254</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3765499827555359</v>
+        <v>-0.359992643455509</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.739064035824804</v>
+        <v>-8.697670687574735</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3451552433196574</v>
+        <v>-0.3285979040196301</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505582813595204</v>
+        <v>-8.464189465345136</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.243838325589965</v>
+        <v>-0.2272809862899381</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.35591642258769</v>
+        <v>-8.314523074337622</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1868639794999187</v>
+        <v>-0.1703066401998914</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223640948956803</v>
+        <v>-8.182247600706734</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1385863033005368</v>
+        <v>-0.1220289640005094</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.033041274283649</v>
+        <v>-7.991647926033582</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0595313727436384</v>
+        <v>-0.0429740334436115</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.784041475600068</v>
+        <v>-7.742648127350001</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0529748879534524</v>
+        <v>0.0695322272534793</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889631465373173</v>
+        <v>-7.848238117123105</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1172370375550078</v>
+        <v>-0.1006796982549809</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-7.866973019241702</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.05962931722533327</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.087258864897787</v>
+        <v>3.094642941031838</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76042632608417</v>
+        <v>-7.719032977834103</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.01726808984962869</v>
+        <v>0.00667332558444933</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.021845652338614</v>
+        <v>2.029229728472665</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.078544878644308</v>
+        <v>3.085928954778359</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.743268175952876</v>
+        <v>-7.701874827702809</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01911881605058952</v>
+        <v>0.004822599383488502</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.023426556163912</v>
+        <v>2.030810632297963</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.071584266549215</v>
+        <v>3.078968342683266</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699719769182185</v>
+        <v>-7.658326420932118</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.008660065437406494</v>
+        <v>0.01528134999667152</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.016465944068819</v>
+        <v>2.02385002020287</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086046620930358</v>
+        <v>3.093430697064409</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457571375728327</v>
+        <v>-7.41617802747826</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1026616463252799</v>
+        <v>0.1266030617593579</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.030928298449962</v>
+        <v>2.038312374584013</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.080578741389553</v>
+        <v>3.087962817523604</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349312238605806</v>
+        <v>-7.307918890355738</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1404974216334836</v>
+        <v>0.1644388370675616</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.025460418909157</v>
+        <v>2.032844495043208</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.07807683540013</v>
+        <v>3.085460911534181</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.226021103788675</v>
+        <v>-7.184627755538608</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1873119695709131</v>
+        <v>0.2112533850049911</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.096933193810012</v>
+        <v>2.104317269944064</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.085777813637455</v>
+        <v>3.093161889771507</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204871904885231</v>
+        <v>-7.163478556635164</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2034726273696155</v>
+        <v>0.2274140428036935</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.117323691389403</v>
+        <v>2.124707767523454</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.081558521984506</v>
+        <v>3.088942598118557</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.961106462901787</v>
+        <v>-6.91971311465172</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.296759512510044</v>
+        <v>0.320700927944122</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.113104399736454</v>
+        <v>2.120488475870505</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.083682835904522</v>
+        <v>3.091066912038573</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859343642624492</v>
+        <v>-6.817950294374425</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3395889545409778</v>
+        <v>0.3635303699750558</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.123160154691927</v>
+        <v>2.130544230825978</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.076424910888224</v>
+        <v>3.083808987022275</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.609493248675418</v>
+        <v>-6.56809990042535</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4322711871043099</v>
+        <v>0.4562126025383879</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.11590222967563</v>
+        <v>2.123286305809681</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080024034408873</v>
+        <v>3.087408110542924</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433601156207985</v>
+        <v>-6.392207807957918</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5062271476119315</v>
+        <v>0.5301685630460096</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.119501353196278</v>
+        <v>2.126885429330329</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.093351540463427</v>
+        <v>3.100735616597478</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.262154693185521</v>
+        <v>-6.220761344935455</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.588133238875471</v>
+        <v>0.6120746543095485</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.23569673706431</v>
+        <v>2.243080813198361</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.092372018079724</v>
+        <v>3.099756094213775</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.037121693516698</v>
+        <v>-5.995728345266632</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.677166916359297</v>
+        <v>0.7011083317933746</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.369737014481901</v>
+        <v>2.377121090615952</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.097066819134041</v>
+        <v>3.104450895268092</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973485951282764</v>
+        <v>-5.932092603032697</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7073160143071879</v>
+        <v>0.731257429741266</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.412613260876578</v>
+        <v>2.41999733701063</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.078261077917837</v>
+        <v>3.085645154051888</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880485910076866</v>
+        <v>-5.839092561826799</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7257102895733429</v>
+        <v>0.7496517050074205</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.393807519660374</v>
+        <v>2.401191595794425</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.080004154542714</v>
+        <v>3.087388230676765</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.640055413272005</v>
+        <v>-5.598662065021939</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8236255649201647</v>
+        <v>0.8475669803542423</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.539808894368168</v>
+        <v>2.547192970502219</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.083933468377534</v>
+        <v>3.091317544511585</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567812845100811</v>
+        <v>-5.526419496850744</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8564519060234628</v>
+        <v>0.8803933214575403</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.543738208202988</v>
+        <v>2.551122284337039</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.084612052294874</v>
+        <v>3.091996128428925</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514814522819423</v>
+        <v>-5.473421174569356</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8783298188533579</v>
+        <v>0.9022712342874355</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.577618547521491</v>
+        <v>2.585002623655543</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.081610123514868</v>
+        <v>3.088994199648919</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.406009637339696</v>
+        <v>-5.364616289089629</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.918849844265242</v>
+        <v>0.9427912596993195</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.574616618741485</v>
+        <v>2.582000694875536</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083189160525482</v>
+        <v>3.090573236659533</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185988839302685</v>
+        <v>-5.144595491052619</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.00843720049066</v>
+        <v>1.032378615924738</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.660927562792887</v>
+        <v>2.668311638926938</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.099083343327305</v>
+        <v>3.106467419461356</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.053121150239408</v>
+        <v>-5.011727801989341</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.077478458917795</v>
+        <v>1.101419874351873</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.67682174559471</v>
+        <v>2.684205821728761</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.100229187767607</v>
+        <v>3.107613263901658</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.893606046720038</v>
+        <v>-4.852212698469971</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142430344765845</v>
+        <v>1.166371760199922</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.773676652146634</v>
+        <v>2.781060728280685</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.110317290329047</v>
+        <v>3.117701366463098</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.7489339016203</v>
+        <v>-4.707540553370234</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.210387305367179</v>
+        <v>1.234328720801257</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.870568041767917</v>
+        <v>2.877952117901968</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.096354781730473</v>
+        <v>3.103738857864524</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808808728977993</v>
+        <v>-4.767415380727926</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.172474865825528</v>
+        <v>1.196416281259606</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.820680636754727</v>
+        <v>2.828064712888778</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.118755275053039</v>
+        <v>3.12613935118709</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.722009231198983</v>
+        <v>-4.680615882948917</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.229595158259698</v>
+        <v>1.253536573693776</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.843081130077293</v>
+        <v>2.850465206211344</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.118827676426451</v>
+        <v>3.126211752560502</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724478937660789</v>
+        <v>-4.683085589410723</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.228679677048388</v>
+        <v>1.252621092482465</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.841671707573622</v>
+        <v>2.849055783707673</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.129834598901153</v>
+        <v>3.137218675035204</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.7928491239848</v>
+        <v>-4.751455775734733</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.212338524993486</v>
+        <v>1.236279940427564</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.858244049470053</v>
+        <v>2.865628125604104</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.120271307533044</v>
+        <v>3.127655383667095</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.901387304900934</v>
+        <v>-4.859993956650867</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.159359961258923</v>
+        <v>1.183301376693001</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.848680758101944</v>
+        <v>2.856064834235995</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.944980872573431</v>
+        <v>2.952364948707482</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.932380464229639</v>
+        <v>-4.890987115979573</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9716722625678282</v>
+        <v>0.9956136780019058</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.673390323142331</v>
+        <v>2.680774399276382</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.949548104565219</v>
+        <v>2.95693218069927</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.75690620443717</v>
+        <v>-4.715512856187104</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.046429198476603</v>
+        <v>1.070370613910681</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.677957555134118</v>
+        <v>2.685341631268169</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.925290133326426</v>
+        <v>2.932674209460477</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.867842457078419</v>
+        <v>-4.826449108828353</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.977796726181311</v>
+        <v>1.001738141615389</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.653699583895325</v>
+        <v>2.661083660029377</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.928421518546331</v>
+        <v>2.935805594680382</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.070869034621652</v>
+        <v>-5.029475686371586</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8997174803839232</v>
+        <v>0.9236588958180008</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.535015022589291</v>
+        <v>2.542399098723342</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.938593904978464</v>
+        <v>2.945977981112515</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.912943435686359</v>
+        <v>-4.871550087436293</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9730601063901727</v>
+        <v>0.9970015218242505</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.545187409021423</v>
+        <v>2.552571485155474</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.933540175552324</v>
+        <v>2.940924251686375</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.826699972659982</v>
+        <v>-4.785306624409915</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.002503762174584</v>
+        <v>1.026445177608662</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.540133679595284</v>
+        <v>2.547517755729335</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.92531595099685</v>
+        <v>2.932700027130901</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.872006792058961</v>
+        <v>-4.830613443808895</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9761568098595177</v>
+        <v>1.000098225293595</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.507423357234271</v>
+        <v>2.514807433368322</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.925867824029951</v>
+        <v>2.933251900164002</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.901039896761263</v>
+        <v>-4.859646548511196</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.965095441011699</v>
+        <v>0.9890368564457765</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.507975230267372</v>
+        <v>2.515359306401423</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.855140515921317</v>
+        <v>2.862524592055368</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.808229415310403</v>
+        <v>-4.766836067060336</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9314923254834084</v>
+        <v>0.955433740917486</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.492934211029254</v>
+        <v>2.500318287163305</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.857013991845918</v>
+        <v>2.864398067979969</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.85261888463983</v>
+        <v>-4.811225536389764</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9156100136762382</v>
+        <v>0.939551429110316</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.468174005356198</v>
+        <v>2.475558081490249</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.852089700357641</v>
+        <v>2.859473776491692</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.73994766640358</v>
+        <v>-4.698554318153514</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9557542094824614</v>
+        <v>0.9796956249165389</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.530852444809671</v>
+        <v>2.538236520943722</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.857580996188308</v>
+        <v>2.864965072322359</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.627570665220907</v>
+        <v>-4.586177316970841</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.006196305786198</v>
+        <v>1.030137721220275</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.536343740640338</v>
+        <v>2.543727816774389</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.869078197956847</v>
+        <v>2.876462274090898</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.825805234107638</v>
+        <v>-4.784411885857572</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9383996800000445</v>
+        <v>0.9623410954341221</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.428900201076839</v>
+        <v>2.43628427721089</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.7074339179575</v>
+        <v>2.714817994091551</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.908806515132917</v>
+        <v>-4.867413166882851</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7435548875905862</v>
+        <v>0.7674963030246638</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.256113390361188</v>
+        <v>2.263497466495239</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.827583578676706</v>
+        <v>2.834967654810757</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.017420593576248</v>
+        <v>-4.976027245326182</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8202589169324592</v>
+        <v>0.844200332366537</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.376263051080393</v>
+        <v>2.383647127214445</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.842096604779029</v>
+        <v>2.84948068091308</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.104019176557351</v>
+        <v>-5.062625828307285</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8001325098423413</v>
+        <v>0.8240739252764189</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.390776077182716</v>
+        <v>2.398160153316768</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.839516046121398</v>
+        <v>2.846900122255449</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.0656355139992</v>
+        <v>-5.024242165749134</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8129054162079701</v>
+        <v>0.8368468316420481</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.411225716059976</v>
+        <v>2.418609792194027</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.836245074966699</v>
+        <v>2.843629151100751</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.888519183964034</v>
+        <v>-4.847125835713967</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8804809770673385</v>
+        <v>0.9044223925014163</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.407954744905278</v>
+        <v>2.415338821039329</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.836928466728613</v>
+        <v>2.844312542862664</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.85881705998774</v>
+        <v>-4.817423711737674</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8930452184197692</v>
+        <v>0.9169866338538468</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.405956061538003</v>
+        <v>2.413340137672054</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.830715442035027</v>
+        <v>2.838099518169078</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.679441638748973</v>
+        <v>-4.638048290498906</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9585823622216907</v>
+        <v>0.9825237776557683</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.493809091746849</v>
+        <v>2.5011931678809</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.811522897366617</v>
+        <v>2.818906973500668</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.724455852269578</v>
+        <v>-4.683062504019512</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.921384132145038</v>
+        <v>0.9453255475791158</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.456407209889675</v>
+        <v>2.463791286023727</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.817214459705562</v>
+        <v>2.824598535839614</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.991460362542013</v>
+        <v>-4.950067014291947</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8202738903750098</v>
+        <v>0.8442153058090875</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.345480949402852</v>
+        <v>2.352865025536903</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.816418381602064</v>
+        <v>2.823802457736115</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.092658143979186</v>
+        <v>-5.05126479572912</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.778998699696642</v>
+        <v>0.8029401151307196</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.303639583172162</v>
+        <v>2.311023659306213</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.814018343156381</v>
+        <v>2.821402419290432</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.060182557808414</v>
+        <v>-5.018789209558348</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7895888957192678</v>
+        <v>0.8135303111533454</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.301239544726479</v>
+        <v>2.30862362086053</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.810543062364625</v>
+        <v>2.817927138498677</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.041144430101117</v>
+        <v>-4.99975108185105</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7937288660104316</v>
+        <v>0.8176702814445092</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.262854097136007</v>
+        <v>2.270238173270058</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.988124931303306</v>
+        <v>2.995509007437357</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.072271061251735</v>
+        <v>-5.030877713001669</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9588600824888647</v>
+        <v>0.9828014979229422</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.440435966074688</v>
+        <v>2.447820042208739</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.98895826028944</v>
+        <v>2.996342336423491</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.124591441852527</v>
+        <v>-5.08319809360246</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9387652592346818</v>
+        <v>0.9627066746687594</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.462237411066144</v>
+        <v>2.469621487200195</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.994966790686366</v>
+        <v>3.002350866820417</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.144848740381485</v>
+        <v>-5.103455392131418</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9366708702200244</v>
+        <v>0.9606122856541019</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.46824594146307</v>
+        <v>2.475630017597121</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.074119438478387</v>
+        <v>3.081503514612439</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.997105770146482</v>
+        <v>-4.955712421896416</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.074920706106047</v>
+        <v>1.098862121540125</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.648083003596022</v>
+        <v>2.655467079730073</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.076913060009868</v>
+        <v>3.08429713614392</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.099120452677703</v>
+        <v>-5.057727104427637</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.03690845462504</v>
+        <v>1.060849870059117</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.650876625127503</v>
+        <v>2.658260701261554</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.077575408401527</v>
+        <v>3.084959484535578</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.962511108583611</v>
+        <v>-4.921117760333544</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.092214540654335</v>
+        <v>1.116155956088413</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.733504579975617</v>
+        <v>2.740888656109668</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.076655885141637</v>
+        <v>3.084039961275688</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.105276441406261</v>
+        <v>-5.063883093156194</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.034188884265385</v>
+        <v>1.058130299699463</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.646925857022137</v>
+        <v>2.654309933156188</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.142991438938458</v>
+        <v>3.150375515072509</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.042978442630139</v>
+        <v>-5.001585094380072</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.125443637572655</v>
+        <v>1.149385053006733</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.713261410818958</v>
+        <v>2.720645486953009</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.851572311327856</v>
+        <v>3.157148186651628</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.841188244964981</v>
+        <v>-4.799794896714914</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9147405890281164</v>
+        <v>1.236873803651915</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.540653198509848</v>
+        <v>2.84622907383362</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.921862543650031</v>
+        <v>3.227438418973803</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.781297563322387</v>
+        <v>-4.739904215072321</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.008987094007329</v>
+        <v>1.331120308631127</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.64687783981758</v>
+        <v>2.952453715141352</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.936490279766075</v>
+        <v>3.242066155089847</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.879038107947362</v>
+        <v>-4.837644759697295</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9845186122733829</v>
+        <v>1.306651826897181</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.651972009053835</v>
+        <v>2.957547884377607</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.935026260590746</v>
+        <v>3.240602135914518</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.055375868070291</v>
+        <v>-5.013982519820225</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9125194890488828</v>
+        <v>1.234652703672681</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.544705333804749</v>
+        <v>2.850281209128521</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.933517878630675</v>
+        <v>3.239093753954447</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.054686495909068</v>
+        <v>-5.013293147659001</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9112868559533007</v>
+        <v>1.233420070577099</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.543196951844678</v>
+        <v>2.84877282716845</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.933380746066111</v>
+        <v>3.238956621389883</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.06125746096366</v>
+        <v>-5.019864112713594</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9085213373668997</v>
+        <v>1.230654551990698</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.539117240247358</v>
+        <v>2.84469311557113</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.933380746066111</v>
+        <v>3.238956621389883</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.053303490668888</v>
+        <v>-5.011910142418822</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9117029254848088</v>
+        <v>1.233836140108607</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.539117240247358</v>
+        <v>2.84469311557113</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.939762503093916</v>
+        <v>3.245338378417688</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.042930114335801</v>
+        <v>-5.001536766085735</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9222340330458478</v>
+        <v>1.244367247669646</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.551723023075015</v>
+        <v>2.857298898398787</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.944654876468641</v>
+        <v>3.250230751792412</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.915245804541505</v>
+        <v>-4.873852456291439</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9782001303382915</v>
+        <v>1.30033334496209</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.633225982326318</v>
+        <v>2.93880185765009</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.931409548944513</v>
+        <v>3.236985424268285</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.975912394943894</v>
+        <v>-4.934519046693827</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9406881666532081</v>
+        <v>1.262821381277007</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.57096166477107</v>
+        <v>2.876537540094842</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.935507251555141</v>
+        <v>3.241083126878913</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.910918535010248</v>
+        <v>-4.869525186760182</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.970783413237295</v>
+        <v>1.292916627861093</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.591157736144192</v>
+        <v>2.896733611467964</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.939668191186219</v>
+        <v>3.245244066509991</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.011677170767246</v>
+        <v>-4.97028382251718</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9346408985655739</v>
+        <v>1.256774113189372</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.542023334539067</v>
+        <v>2.847599209862838</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.945547793714057</v>
+        <v>3.251123669037828</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.967474333681346</v>
+        <v>-4.926080985431279</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.958201635927771</v>
+        <v>1.280334850551569</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.574424639318444</v>
+        <v>2.880000514642216</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.943957794183304</v>
+        <v>3.249533669507076</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.004453361344789</v>
+        <v>-4.963060013094722</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9418200253316416</v>
+        <v>1.26395323995544</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.59501898086249</v>
+        <v>2.900594856186262</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,45 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.760495499820589</v>
+        <v>3.863924114042144</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.995205559366344</v>
+        <v>3.300781434690116</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.024511440209629</v>
+        <v>-4.983118091959563</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9850445589687449</v>
+        <v>1.307177773592543</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.64626674604553</v>
+        <v>2.951842621369301</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="2" t="n">
+        <v>45448</v>
+      </c>
+      <c r="B1986" t="n">
+        <v>3.763086566094771</v>
+      </c>
+      <c r="C1986" t="n">
+        <v>3.180483142682065</v>
+      </c>
+      <c r="D1986" t="n">
+        <v>-4.983118091959563</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>1.307177773592543</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>-0.5815646888680245</v>
+      </c>
+      <c r="G1986" t="n">
+        <v>3.173546939668433</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>-25.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-682.1%</t>
+          <t>-686.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>453.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.9%</t>
+          <t>-673.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.2%</t>
+          <t>-274.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.5%</t>
+          <t>-293.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-156.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-288.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-128.7%</t>
+          <t>-160.3%</t>
         </is>
       </c>
     </row>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.732584176345583</v>
+        <v>-3.773977524595651</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.644700442900265</v>
+        <v>1.628143103600238</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.3767926242528168</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.076266949572246</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.508996457064216</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.484698676280035</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.282778726459267</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.422497804965666</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6912104531670565</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.53861981223796</v>
+        <v>-4.580013160488028</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.321934297354448</v>
+        <v>1.305376958054421</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6912104531670565</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.970425605387748</v>
+        <v>-5.011818953637816</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.135544867561938</v>
+        <v>1.11898752826191</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8276279496083235</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.2051195995203</v>
+        <v>-5.246512947770368</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.029952044911007</v>
+        <v>1.01339470561098</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8212916823790684</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.540782246750752</v>
+        <v>-5.582175595000821</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8942675776747913</v>
+        <v>0.8777102383747644</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8212916823790684</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.904408491651066</v>
+        <v>-5.945801839901134</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7553046399489078</v>
+        <v>0.7387473006488805</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9195133192461942</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.269535874289812</v>
+        <v>-6.310929222539881</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6085082018992405</v>
+        <v>0.5919508625992131</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.215824103545207</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.67812465147049</v>
+        <v>-6.719517999720559</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4438342350417281</v>
+        <v>0.4272768957417008</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.624412880725885</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.954700751786323</v>
+        <v>-6.996094100036391</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3283892273868556</v>
+        <v>0.3118318880868287</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.37109262607332</v>
+        <v>-7.412485974323388</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1598265282809344</v>
+        <v>0.143269188980907</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.687704568613968</v>
+        <v>-7.729097916864037</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04344044193335383</v>
+        <v>0.02688310263332649</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.033579390598778</v>
+        <v>-8.074972738848846</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09880992171487479</v>
+        <v>-0.1153672610149017</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.197159268783162</v>
+        <v>-8.23855261703323</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1658369529336272</v>
+        <v>-0.1823942922336546</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.49382061059336</v>
+        <v>-8.535213958843428</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2807225137284983</v>
+        <v>-0.2972798530285257</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.698851791367677</v>
+        <v>-8.740245139617745</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3667612905726281</v>
+        <v>-0.3833186298726554</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.081853180110308</v>
+        <v>-9.123246528360376</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5200639473912645</v>
+        <v>-0.5366212866912918</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.263722971095342</v>
+        <v>-9.305116319345411</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5902403478138485</v>
+        <v>-0.6067976871138758</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.623253293599344</v>
+        <v>-9.664646641849412</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7287021735173989</v>
+        <v>-0.7452595128174262</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.673602357053566</v>
+        <v>-9.714995705303634</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7409257789419104</v>
+        <v>-0.7574831182419373</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.771221634474962</v>
+        <v>-9.81261498272503</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7769317392886999</v>
+        <v>-0.7934890785887272</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.918747722480605</v>
+        <v>-9.960141070730673</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8330486181693848</v>
+        <v>-0.8496059574694121</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.12300589781047</v>
+        <v>-10.16439924606054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9092386911826882</v>
+        <v>-0.9257960304827151</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.26481567201726</v>
+        <v>-10.30620902026732</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.961480046380967</v>
+        <v>-0.9780373856809939</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.19134584034981</v>
+        <v>-10.23273918859988</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9167204122205659</v>
+        <v>-0.9332777515205937</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.36647025773635</v>
+        <v>-10.40786360598642</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9722149584276671</v>
+        <v>-0.988772297727694</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.60092235175084</v>
+        <v>-10.64231570000091</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.073214960935058</v>
+        <v>-1.089772300235086</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.88872619628808</v>
+        <v>-10.93011954453815</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.19500868952393</v>
+        <v>-1.211566028823957</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.94151235188841</v>
+        <v>-10.98290570013847</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.215007361925505</v>
+        <v>-1.231564701225532</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.0675491452567</v>
+        <v>-11.10894249350676</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.262728350643706</v>
+        <v>-1.279285689943733</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.01553363128788</v>
+        <v>-11.05692697953795</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.23793180936978</v>
+        <v>-1.254489148669807</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.157205473012</v>
+        <v>-11.19859882126207</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.29607577295817</v>
+        <v>-1.312633112258196</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.10761462858717</v>
+        <v>-11.14900797683724</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.261186025023364</v>
+        <v>-1.277743364323391</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.09480723558239</v>
+        <v>-11.13620058383246</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.269114201468137</v>
+        <v>-1.285671540768164</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.86896208286298</v>
+        <v>-10.91035543111305</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.169197067344163</v>
+        <v>-1.185754406644191</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.74438342652539</v>
+        <v>-10.78577677477546</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.118226460253068</v>
+        <v>-1.134783799553095</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.79727871456968</v>
+        <v>-10.83867206281974</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.136750801308675</v>
+        <v>-1.153308140608702</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.51336998364093</v>
+        <v>-10.554763331891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.017453604698539</v>
+        <v>-1.034010943998566</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.44200359103128</v>
+        <v>-10.48339693928135</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9986443100485447</v>
+        <v>-1.015201649348572</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17816672382721</v>
+        <v>-10.21956007207728</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9029930444798242</v>
+        <v>-0.919550383779852</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910924922958813</v>
+        <v>-9.952318271208881</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7979308846318394</v>
+        <v>-0.8144882239318663</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.813017884282322</v>
+        <v>-9.85441123253239</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7590683841347037</v>
+        <v>-0.775625723434731</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.789064343306364</v>
+        <v>-9.830457691556433</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7488184615988271</v>
+        <v>-0.765375800898854</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.525004404983568</v>
+        <v>-9.566397753233636</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6564548024314605</v>
+        <v>-0.6730121417314878</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.81792478147873</v>
+        <v>-8.859318129728798</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3764099866898265</v>
+        <v>-0.3929673259898534</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.77774048311254</v>
+        <v>-8.819133831362608</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.359992643455509</v>
+        <v>-0.3765499827555359</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.697670687574735</v>
+        <v>-8.739064035824804</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3285979040196301</v>
+        <v>-0.3451552433196574</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.464189465345136</v>
+        <v>-8.505582813595204</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2272809862899381</v>
+        <v>-0.243838325589965</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.314523074337622</v>
+        <v>-8.35591642258769</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1703066401998914</v>
+        <v>-0.1868639794999187</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.182247600706734</v>
+        <v>-8.223640948956803</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1220289640005094</v>
+        <v>-0.1385863033005368</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.991647926033582</v>
+        <v>-8.033041274283649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0429740334436115</v>
+        <v>-0.0595313727436384</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.742648127350001</v>
+        <v>-7.784041475600068</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0695322272534793</v>
+        <v>0.0529748879534524</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.848238117123105</v>
+        <v>-7.889631465373173</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1006796982549809</v>
+        <v>-0.1172370375550078</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.866973019241702</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05962931722533327</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.094642941031838</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.719032977834103</v>
+        <v>-7.846496977136879</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.00667332558444933</v>
+        <v>-0.171317823071572</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.775688687598622</v>
+        <v>-1.834232881885876</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.029229728472665</v>
+        <v>1.867097662965402</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.085928954778359</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.701874827702809</v>
+        <v>-7.829338827005585</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.004822599383488502</v>
+        <v>-0.1731685492725323</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.817074731754582</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.030810632297963</v>
+        <v>1.8686785667907</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.078968342683266</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.658326420932118</v>
+        <v>-7.785790420234894</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01528134999667152</v>
+        <v>-0.1627097986593493</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.817074731754582</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.02385002020287</v>
+        <v>1.861717954695607</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.093430697064409</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.41617802747826</v>
+        <v>-7.543642026781036</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1266030617593579</v>
+        <v>-0.05138808689666297</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.817074731754582</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.038312374584013</v>
+        <v>1.87618030907675</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.087962817523604</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.307918890355738</v>
+        <v>-7.435382889658515</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1644388370675616</v>
+        <v>-0.01355231158845926</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.758530537467328</v>
+        <v>-1.817074731754582</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.032844495043208</v>
+        <v>1.870712429535945</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.085460911534181</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.184627755538608</v>
+        <v>-7.312091754841384</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2112533850049911</v>
+        <v>0.03326223634896985</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.635239402650197</v>
+        <v>-1.693783596937452</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.104317269944064</v>
+        <v>1.9421852044368</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.093161889771507</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.163478556635164</v>
+        <v>-7.29094255593794</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2274140428036935</v>
+        <v>0.04942289414767265</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.672634398034008</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.124707767523454</v>
+        <v>1.962575702016192</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.088942598118557</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.91971311465172</v>
+        <v>-7.047177113954496</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.320700927944122</v>
+        <v>0.1427097792881011</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.614090203746754</v>
+        <v>-1.672634398034008</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.120488475870505</v>
+        <v>1.958356410363242</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.091066912038573</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.817950294374425</v>
+        <v>-6.945414293677201</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3635303699750558</v>
+        <v>0.185539221319035</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.659415329641579</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.130544230825978</v>
+        <v>1.968412165318715</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.083808987022275</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.56809990042535</v>
+        <v>-6.695563899728127</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4562126025383879</v>
+        <v>0.2782214538823671</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.659415329641579</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.123286305809681</v>
+        <v>1.961154240302418</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.087408110542924</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.392207807957918</v>
+        <v>-6.519671807260695</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5301685630460096</v>
+        <v>0.3521774143899883</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.600871135354325</v>
+        <v>-1.659415329641579</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.126885429330329</v>
+        <v>1.964753363823066</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.100735616597478</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.220761344935455</v>
+        <v>-6.348225344238231</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6120746543095485</v>
+        <v>0.4340835056535277</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.429424672331862</v>
+        <v>-1.487968866619116</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.243080813198361</v>
+        <v>2.080948747691098</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.099756094213775</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.995728345266632</v>
+        <v>-6.123192344569408</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7011083317933746</v>
+        <v>0.5231171831373538</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.204391672663039</v>
+        <v>-1.262935866950293</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.377121090615952</v>
+        <v>2.214989025108689</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.104450895268092</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.932092603032697</v>
+        <v>-6.059556602335474</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.731257429741266</v>
+        <v>0.5532662810852447</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.199300124716359</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.41999733701063</v>
+        <v>2.257865271503367</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.085645154051888</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.839092561826799</v>
+        <v>-5.966556561129575</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7496517050074205</v>
+        <v>0.5716605563513997</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.140755930429105</v>
+        <v>-1.199300124716359</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.401191595794425</v>
+        <v>2.239059530287162</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.087388230676765</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.598662065021939</v>
+        <v>-5.726126064324715</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8475669803542423</v>
+        <v>0.6695758316982214</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9588696279114985</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.547192970502219</v>
+        <v>2.385060904994956</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.091317544511585</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.526419496850744</v>
+        <v>-5.65388349615352</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8803933214575403</v>
+        <v>0.7024021728015195</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9003254336242443</v>
+        <v>-0.9588696279114985</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.551122284337039</v>
+        <v>2.388990218829776</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.091996128428925</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.473421174569356</v>
+        <v>-5.600885173872133</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9022712342874355</v>
+        <v>0.7242800856314147</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.9035333689095597</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.585002623655543</v>
+        <v>2.422870558148279</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.088994199648919</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.364616289089629</v>
+        <v>-5.492080288392406</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9427912596993195</v>
+        <v>0.7648001110432987</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8449891746223055</v>
+        <v>-0.9035333689095597</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.582000694875536</v>
+        <v>2.419868629368273</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.090573236659533</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.144595491052619</v>
+        <v>-5.272059490355395</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.032378615924738</v>
+        <v>0.8543874672687171</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7623135238415795</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.668311638926938</v>
+        <v>2.506179573419675</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.106467419461356</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.011727801989341</v>
+        <v>-5.139191801292117</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.101419874351873</v>
+        <v>0.9234287256958513</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7037693295543253</v>
+        <v>-0.7623135238415795</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.684205821728761</v>
+        <v>2.522073756221499</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.107613263901658</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.852212698469971</v>
+        <v>-4.979676697772748</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.166371760199922</v>
+        <v>0.9883806115439013</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5442542260349553</v>
+        <v>-0.6027984203222095</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.781060728280685</v>
+        <v>2.618928662773422</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.117701366463098</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.707540553370234</v>
+        <v>-4.83500455267301</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.234328720801257</v>
+        <v>1.056337572145236</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3995820809352179</v>
+        <v>-0.4581262752224721</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.877952117901968</v>
+        <v>2.715820052394704</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.103738857864524</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.767415380727926</v>
+        <v>-4.894879380030702</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.196416281259606</v>
+        <v>1.018425132603585</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5180011025801643</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.828064712888778</v>
+        <v>2.665932647381515</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.12613935118709</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.680615882948917</v>
+        <v>-4.808079882251693</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.253536573693776</v>
+        <v>1.075545425037755</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.45945690829291</v>
+        <v>-0.5180011025801643</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.850465206211344</v>
+        <v>2.688333140704081</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.126211752560502</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.683085589410723</v>
+        <v>-4.810549588713499</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.252621092482465</v>
+        <v>1.074629943826445</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4619266147547162</v>
+        <v>-0.5204708090419705</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.849055783707673</v>
+        <v>2.68692371820041</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.137218675035204</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.751455775734733</v>
+        <v>-4.87891977503751</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.236279940427564</v>
+        <v>1.058288791771542</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5111951100057556</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.865628125604104</v>
+        <v>2.703496060096841</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.127655383667095</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.859993956650867</v>
+        <v>-4.991414914404595</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.183301376693001</v>
+        <v>1.0037274446566</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5111951100057556</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.856064834235995</v>
+        <v>2.693932768728732</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.952364948707482</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.890987115979573</v>
+        <v>-5.0224080737333</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9956136780019058</v>
+        <v>0.8160397459655044</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5111951100057556</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.680774399276382</v>
+        <v>2.518642333769119</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.95693218069927</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.715512856187104</v>
+        <v>-4.846933813940831</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.070370613910681</v>
+        <v>0.8907966818742796</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5111951100057556</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.685341631268169</v>
+        <v>2.523209565760907</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.932674209460477</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.826449108828353</v>
+        <v>-4.95787006658208</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.001738141615389</v>
+        <v>0.8221642095789872</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4526509157185012</v>
+        <v>-0.5111951100057556</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.661083660029377</v>
+        <v>2.498951594522114</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.935805594680382</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.029475686371586</v>
+        <v>-5.160896644125313</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9236588958180008</v>
+        <v>0.7440849637815994</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.714221687548989</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.542399098723342</v>
+        <v>2.380267033216079</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.945977981112515</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.871550087436293</v>
+        <v>-5.00297104519002</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9970015218242505</v>
+        <v>0.8174275897878491</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.714221687548989</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.552571485155474</v>
+        <v>2.390439419648211</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.940924251686375</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.785306624409915</v>
+        <v>-4.916727582163642</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.026445177608662</v>
+        <v>0.8468712455722605</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6556774932617346</v>
+        <v>-0.714221687548989</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.547517755729335</v>
+        <v>2.385385690222072</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.932700027130901</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.830613443808895</v>
+        <v>-4.962034401562622</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.000098225293595</v>
+        <v>0.8205242932571941</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7550318505582198</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.514807433368322</v>
+        <v>2.352675367861059</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.933251900164002</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.859646548511196</v>
+        <v>-4.991067506264923</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9890368564457765</v>
+        <v>0.8094629244093752</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6964876562709654</v>
+        <v>-0.7550318505582198</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.515359306401423</v>
+        <v>2.353227240894161</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.862524592055368</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.766836067060336</v>
+        <v>-4.898257024814064</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.955433740917486</v>
+        <v>0.7758598088810846</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6036771748201061</v>
+        <v>-0.6622213691073604</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.500318287163305</v>
+        <v>2.338186221656041</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.864398067979969</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.811225536389764</v>
+        <v>-4.942646494143491</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.939551429110316</v>
+        <v>0.7599774970739146</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6480666441495337</v>
+        <v>-0.7066108384367881</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.475558081490249</v>
+        <v>2.313426015982986</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.859473776491692</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.698554318153514</v>
+        <v>-4.829975275907241</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9796956249165389</v>
+        <v>0.8001216928801376</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5939396202005378</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.538236520943722</v>
+        <v>2.376104455436459</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.864965072322359</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.586177316970841</v>
+        <v>-4.717598274724568</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.030137721220275</v>
+        <v>0.850563789183874</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5353954259132836</v>
+        <v>-0.5939396202005378</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.543727816774389</v>
+        <v>2.381595751267126</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.876462274090898</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.784411885857572</v>
+        <v>-4.915832843611299</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9623410954341221</v>
+        <v>0.7827671633977207</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7336299948000142</v>
+        <v>-0.7921741890872684</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.43628427721089</v>
+        <v>2.274152211703627</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.714817994091551</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.867413166882851</v>
+        <v>-4.998834124636578</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7674963030246638</v>
+        <v>0.5879223709882624</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8107450736144421</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.263497466495239</v>
+        <v>2.101365400987976</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.834967654810757</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.976027245326182</v>
+        <v>-5.107448203079909</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.844200332366537</v>
+        <v>0.6646264003301354</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8107450736144421</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.383647127214445</v>
+        <v>2.221515061707182</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.84948068091308</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.062625828307285</v>
+        <v>-5.194046786061012</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8240739252764189</v>
+        <v>0.6444999932400175</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7522008793271879</v>
+        <v>-0.8107450736144421</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.398160153316768</v>
+        <v>2.236028087809505</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.846900122255449</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.024242165749134</v>
+        <v>-5.155663123502861</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8368468316420481</v>
+        <v>0.6572728996056467</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.772361411056291</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.418609792194027</v>
+        <v>2.256477726686764</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.843629151100751</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.847125835713967</v>
+        <v>-4.978546793467695</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9044223925014163</v>
+        <v>0.7248484604650149</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.7138172167690368</v>
+        <v>-0.772361411056291</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.415338821039329</v>
+        <v>2.253206755532066</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.844312542862664</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.817423711737674</v>
+        <v>-4.948844669491401</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9169866338538468</v>
+        <v>0.7374127018174454</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7182873419843501</v>
+        <v>-0.7768315362716043</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.413340137672054</v>
+        <v>2.251208072164791</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.838099518169078</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.638048290498906</v>
+        <v>-4.769469248252634</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9825237776557683</v>
+        <v>0.8029498456193669</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5615105838136314</v>
+        <v>-0.6200547781008856</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.5011931678809</v>
+        <v>2.339061102373637</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.818906973500668</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.683062504019512</v>
+        <v>-4.814483461773239</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9453255475791158</v>
+        <v>0.7657516155427144</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.591859479128236</v>
+        <v>-0.6504036734154902</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.463791286023727</v>
+        <v>2.301659220516464</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.824598535839614</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.950067014291947</v>
+        <v>-5.081487972045674</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8442153058090875</v>
+        <v>0.6646413737726862</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7862225171711845</v>
+        <v>-0.8447667114584387</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.352865025536903</v>
+        <v>2.19073296002964</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.823802457736115</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.05126479572912</v>
+        <v>-5.182685753482847</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8029401151307196</v>
+        <v>0.6233661830943182</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.9131755250037579</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.311023659306213</v>
+        <v>2.14889159379895</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.821402419290432</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.018789209558348</v>
+        <v>-5.150210167312075</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8135303111533454</v>
+        <v>0.633956379116944</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.8546313307165037</v>
+        <v>-0.9131755250037579</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.30862362086053</v>
+        <v>2.146491555353267</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.817927138498677</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.99975108185105</v>
+        <v>-5.131172039604778</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8176702814445092</v>
+        <v>0.6380963494081078</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9713591363349524</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.270238173270058</v>
+        <v>2.108106107762795</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.995509007437357</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.030877713001669</v>
+        <v>-5.162298670755396</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9828014979229422</v>
+        <v>0.8032275658865409</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9128149420476982</v>
+        <v>-0.9713591363349524</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.447820042208739</v>
+        <v>2.285687976701475</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.996342336423491</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.08319809360246</v>
+        <v>-5.214619051356188</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9627066746687594</v>
+        <v>0.783132742632358</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9364122763260803</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.469621487200195</v>
+        <v>2.307489421692932</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.002350866820417</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.103455392131418</v>
+        <v>-5.234876349885146</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9606122856541019</v>
+        <v>0.7810383536177006</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.877868082038826</v>
+        <v>-0.9364122763260803</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.475630017597121</v>
+        <v>2.313497952089858</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.081503514612439</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.955712421896416</v>
+        <v>-5.087133379650143</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.098862121540125</v>
+        <v>0.9192881895037237</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.7686049190911971</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.655467079730073</v>
+        <v>2.49333501422281</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.08429713614392</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.057727104427637</v>
+        <v>-5.189148062181364</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.060849870059117</v>
+        <v>0.881275938022716</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7100607248039429</v>
+        <v>-0.7686049190911971</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.658260701261554</v>
+        <v>2.496128635754291</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.084959484535578</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.921117760333544</v>
+        <v>-5.052538718087272</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.116155956088413</v>
+        <v>0.9365820240520115</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.5734513807098505</v>
+        <v>-0.6319955749971047</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.740888656109668</v>
+        <v>2.578756590602405</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.084039961275688</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.063883093156194</v>
+        <v>-5.195304050909922</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.058130299699463</v>
+        <v>0.8785563676630619</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.774760907819755</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.654309933156188</v>
+        <v>2.492177867648925</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.150375515072509</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.001585094380072</v>
+        <v>-5.133006052133799</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.149385053006733</v>
+        <v>0.9698111209703315</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7162167135325008</v>
+        <v>-0.774760907819755</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.720645486953009</v>
+        <v>2.558513421445746</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.157148186651628</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.799794896714914</v>
+        <v>-4.931215854468642</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.236873803651915</v>
+        <v>0.7591080724257928</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5181985213633464</v>
+        <v>-0.5767427156506006</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.84622907383362</v>
+        <v>2.385905209136637</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.227438418973803</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.739904215072321</v>
+        <v>-4.871325172826048</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.331120308631127</v>
+        <v>0.8533545774050053</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.458307839720753</v>
+        <v>-0.5168520340080072</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.952453715141352</v>
+        <v>2.492129850444368</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.242066155089847</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.837644759697295</v>
+        <v>-4.969065717451023</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.306651826897181</v>
+        <v>0.8288860956710591</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.4741971178537331</v>
+        <v>-0.5327413121409874</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.957547884377607</v>
+        <v>2.497224019680623</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.240602135914518</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.013982519820225</v>
+        <v>-5.145403477573952</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.234652703672681</v>
+        <v>0.756886972446559</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.7090790722639169</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.850281209128521</v>
+        <v>2.389957344431537</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.239093753954447</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.013293147659001</v>
+        <v>-5.144714105412729</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.233420070577099</v>
+        <v>0.7556543393509769</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.6505348779766625</v>
+        <v>-0.7090790722639169</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.84877282716845</v>
+        <v>2.388448962471466</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.238956621389883</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.019864112713594</v>
+        <v>-5.151285070467321</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.230654551990698</v>
+        <v>0.7528888207645759</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.7156500373185097</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.84469311557113</v>
+        <v>2.384369250874146</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.238956621389883</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.011910142418822</v>
+        <v>-5.143331100172549</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.233836140108607</v>
+        <v>0.756070408882485</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.6571058430312555</v>
+        <v>-0.7156500373185097</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.84469311557113</v>
+        <v>2.384369250874146</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.245338378417688</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.001536766085735</v>
+        <v>-5.132957723839462</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.244367247669646</v>
+        <v>0.7666015164435245</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.6467324666981682</v>
+        <v>-0.7052766609854224</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.857298898398787</v>
+        <v>2.396975033701803</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.250230751792412</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.873852456291439</v>
+        <v>-5.005273414045166</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.30033334496209</v>
+        <v>0.8225676137359677</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5190481569038717</v>
+        <v>-0.577592351191126</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.93880185765009</v>
+        <v>2.478477992953106</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.236985424268285</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.934519046693827</v>
+        <v>-5.065940004447555</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.262821381277007</v>
+        <v>0.7850556500508845</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6007464736224054</v>
+        <v>-0.6592906679096596</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.876537540094842</v>
+        <v>2.416213675397858</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.241083126878913</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.869525186760182</v>
+        <v>-5.000946144513909</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.292916627861093</v>
+        <v>0.8151508966349712</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.57391585901825</v>
+        <v>-0.6324600533055043</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.896733611467964</v>
+        <v>2.43640974677098</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.245244066509991</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.97028382251718</v>
+        <v>-5.101704780270907</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.256774113189372</v>
+        <v>0.7790083819632501</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.6627414277452555</v>
+        <v>-0.7212856220325097</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.847599209862838</v>
+        <v>2.387275345165855</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.251123669037828</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.926080985431279</v>
+        <v>-5.057501943185007</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.280334850551569</v>
+        <v>0.8025691193254474</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.618538590659355</v>
+        <v>-0.6770827849466092</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.880000514642216</v>
+        <v>2.419676649945232</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.249533669507076</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.963060013094722</v>
+        <v>-5.09448097084845</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.26395323995544</v>
+        <v>0.7861875087293178</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.6401088831552787</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.900594856186262</v>
+        <v>2.440270991489278</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042144</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.300781434690116</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.983118091959563</v>
+        <v>-5.11453904971329</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.307177773592543</v>
+        <v>0.8294120423664211</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.6401088831552787</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.951842621369301</v>
+        <v>2.491518756672318</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.763086566094771</v>
+        <v>3.844986470221169</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.180483142682065</v>
+        <v>2.864629961470227</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.983118091959563</v>
+        <v>-5.11453904971329</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.307177773592543</v>
+        <v>0.8294120423664211</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5815646888680245</v>
+        <v>-0.6401088831552787</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.173546939668433</v>
+        <v>2.857693758456595</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-48.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.9%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.0%</t>
+          <t>-683.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-163.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-293.3%</t>
+          <t>-297.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-295.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.5%</t>
+          <t>-148.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-288.0%</t>
+          <t>-291.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.1%</t>
+          <t>-177.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-183.5%</t>
         </is>
       </c>
     </row>
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117660297822314</v>
+        <v>-4.117349142183405</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492439117764189</v>
+        <v>1.492563580019753</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.484698676280035</v>
+        <v>-0.3743635145062945</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.849040455438841</v>
+        <v>2.915241552503085</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.324172074709336</v>
+        <v>-4.323860919070427</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.405940465665638</v>
+        <v>1.406064927921202</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.580875291393316</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721239447962886</v>
+        <v>2.787440545027131</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.580013160488028</v>
+        <v>-4.579702004849119</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.305376958054421</v>
+        <v>1.305501420309984</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6912104531670565</v>
+        <v>-0.580875291393316</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723012374663146</v>
+        <v>2.78921347172739</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.011818953637816</v>
+        <v>-5.011507797998907</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.11898752826191</v>
+        <v>1.119111990517474</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8276279496083235</v>
+        <v>-0.7172927878345829</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.62749476426579</v>
+        <v>2.693695861330034</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.246512947770368</v>
+        <v>-5.246201792131459</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.01339470561098</v>
+        <v>1.013519167866543</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.7109565206053278</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.619581299605434</v>
+        <v>2.685782396669678</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.582175595000821</v>
+        <v>-5.581864439361912</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8777102383747644</v>
+        <v>0.8778347006303275</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8212916823790684</v>
+        <v>-0.7109565206053278</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.618161891261399</v>
+        <v>2.684362988325643</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.945801839901134</v>
+        <v>-5.945490684262225</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7387473006488805</v>
+        <v>0.7388717629044441</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9195133192461942</v>
+        <v>-0.8091781574724536</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.565716469375365</v>
+        <v>2.63191756643961</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.310929222539881</v>
+        <v>-6.310618066900972</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5919508625992131</v>
+        <v>0.5920753248547768</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.215824103545207</v>
+        <v>-1.105488941771466</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.387184513801789</v>
+        <v>2.453385610866033</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.719517999720559</v>
+        <v>-6.719206844081651</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4272768957417008</v>
+        <v>0.427401357997264</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.140792791508141</v>
+        <v>2.206993888572385</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.996094100036391</v>
+        <v>-6.995782944397483</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3118318880868287</v>
+        <v>0.3119563503423919</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.135978223979602</v>
+        <v>2.202179321043846</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.412485974323388</v>
+        <v>-7.41217481868448</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.143269188980907</v>
+        <v>0.1433936512364702</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.133972274588479</v>
+        <v>2.200173371652723</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.729097916864037</v>
+        <v>-7.728786761225129</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.02688310263332649</v>
+        <v>0.02700756488888967</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.144230965257158</v>
+        <v>2.210432062321402</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.074972738848846</v>
+        <v>-8.074661583209938</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1153672610149017</v>
+        <v>-0.1152427987593385</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.140330530402853</v>
+        <v>2.206531627467097</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.23855261703323</v>
+        <v>-8.238241461394322</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1823942922336546</v>
+        <v>-0.1822698299780914</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.624412880725885</v>
+        <v>-1.514077718952145</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.138735450457854</v>
+        <v>2.204936547522098</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.535213958843428</v>
+        <v>-8.53490280320452</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2972798530285257</v>
+        <v>-0.2971553907729625</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.582820854686023</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.101268544946735</v>
+        <v>2.167469642010979</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.740245139617745</v>
+        <v>-8.739933983978837</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3833186298726554</v>
+        <v>-0.3831941676170922</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.582820854686023</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.097242240412332</v>
+        <v>2.163443337476576</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.123246528360376</v>
+        <v>-9.122935372721468</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5366212866912918</v>
+        <v>-0.5364968244357287</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.693156016459764</v>
+        <v>-1.582820854686023</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.097140139090748</v>
+        <v>2.163341236154992</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.305116319345411</v>
+        <v>-9.304805163706503</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6067976871138758</v>
+        <v>-0.6066732248583127</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.764690645671058</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.990589780471157</v>
+        <v>2.056790877535401</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.664646641849412</v>
+        <v>-9.664335486210504</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7452595128174262</v>
+        <v>-0.745135050561863</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.875025807444799</v>
+        <v>-1.764690645671058</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.995940083769207</v>
+        <v>2.062141180833452</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714995705303634</v>
+        <v>-9.714684549664726</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7574831182419373</v>
+        <v>-0.7573586559863741</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.925374870899021</v>
+        <v>-1.81503970912528</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.973646665653852</v>
+        <v>2.039847762718096</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.81261498272503</v>
+        <v>-9.812303827086122</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7934890785887272</v>
+        <v>-0.793364616333164</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.022994148320417</v>
+        <v>-1.912658986546677</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.918116849822782</v>
+        <v>1.984317946887026</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.960141070730673</v>
+        <v>-9.959829915091765</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8496059574694121</v>
+        <v>-0.849481495213849</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.170520236326061</v>
+        <v>-2.06018507455232</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.832494753340968</v>
+        <v>1.898695850405213</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16439924606054</v>
+        <v>-10.16408809042163</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9257960304827151</v>
+        <v>-0.9256715682271519</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.29815918094005</v>
+        <v>-2.187824019166309</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.761424583691217</v>
+        <v>1.827625680755462</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30620902026732</v>
+        <v>-10.30589786462842</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9780373856809939</v>
+        <v>-0.9779129234254307</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.469437978585626</v>
+        <v>-2.359102816811885</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.663139859588308</v>
+        <v>1.729340956652552</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23273918859988</v>
+        <v>-10.23242803296097</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9332777515205937</v>
+        <v>-0.9331532892650305</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.395968146918177</v>
+        <v>-2.285632985144436</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.722593460082198</v>
+        <v>1.788794557146443</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40786360598642</v>
+        <v>-10.40755245034751</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.988772297727694</v>
+        <v>-0.9886478354721309</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.46075740253098</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.632074030397789</v>
+        <v>1.698275127462033</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.64231570000091</v>
+        <v>-10.642004544362</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089772300235086</v>
+        <v>-1.089647837979523</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.571092564304721</v>
+        <v>-2.46075740253098</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.624854865496193</v>
+        <v>1.691055962560437</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.93011954453815</v>
+        <v>-10.92980838889924</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211566028823957</v>
+        <v>-1.211441566568394</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.858896408841959</v>
+        <v>-2.748561247068218</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.445500367999874</v>
+        <v>1.511701465064118</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98290570013847</v>
+        <v>-10.98259454449957</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231564701225532</v>
+        <v>-1.231440238969968</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.954571895424356</v>
+        <v>-2.844236733650615</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.389210865888992</v>
+        <v>1.455411962953236</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10894249350676</v>
+        <v>-11.10863133786786</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.279285689943733</v>
+        <v>-1.279161227688169</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.818985110840873</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.407055568203952</v>
+        <v>1.473256665268196</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05692697953795</v>
+        <v>-11.05661582389904</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254489148669807</v>
+        <v>-1.254364686414243</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.818985110840873</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.411045903890353</v>
+        <v>1.477247000954597</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19859882126207</v>
+        <v>-11.19828766562316</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312633112258196</v>
+        <v>-1.312508650002633</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.929320272614614</v>
+        <v>-2.818985110840873</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.409570676991611</v>
+        <v>1.475771774055855</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14900797683724</v>
+        <v>-11.14869682119833</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277743364323391</v>
+        <v>-1.277618902067827</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.87972942818978</v>
+        <v>-2.769394266416039</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.454378593811384</v>
+        <v>1.520579690875628</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13620058383246</v>
+        <v>-11.13588942819355</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285671540768164</v>
+        <v>-1.285547078512601</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.928585203198681</v>
+        <v>-2.81825004142494</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.41201399515936</v>
+        <v>1.478215092223604</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91035543111305</v>
+        <v>-10.91004427547414</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185754406644191</v>
+        <v>-1.185629944388628</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.776323365837777</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.446749073547867</v>
+        <v>1.512950170612111</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78577677477546</v>
+        <v>-10.78546561913655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134783799553095</v>
+        <v>-1.134659337297532</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.886658527611517</v>
+        <v>-2.776323365837777</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.447888218103926</v>
+        <v>1.51408931516817</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83867206281974</v>
+        <v>-10.83836090718084</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153308140608702</v>
+        <v>-1.153183678353138</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.77136801974933</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.453495199919101</v>
+        <v>1.519696296983345</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.554763331891</v>
+        <v>-10.55445217625209</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.034010943998566</v>
+        <v>-1.033886481743003</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.881703181523071</v>
+        <v>-2.77136801974933</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.459228904157738</v>
+        <v>1.525430001221982</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48339693928135</v>
+        <v>-10.48308578364244</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.015201649348572</v>
+        <v>-1.015077187093009</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.700001627139682</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.492311477329662</v>
+        <v>1.558512574393906</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21956007207728</v>
+        <v>-10.21924891643837</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.919550383779852</v>
+        <v>-0.9194259215242888</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.700001627139682</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.482427996016754</v>
+        <v>1.548629093080998</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.952318271208881</v>
+        <v>-9.952007115569973</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8144882239318663</v>
+        <v>-0.8143637616763031</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.810336788913423</v>
+        <v>-2.700001627139682</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.48059343551738</v>
+        <v>1.546794532581624</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.85441123253239</v>
+        <v>-9.854100076893483</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.775625723434731</v>
+        <v>-0.7755012611791678</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.742351039052866</v>
+        <v>-2.632015877279126</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.521084570460253</v>
+        <v>1.587285667524497</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.830457691556433</v>
+        <v>-9.830146535917525</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.765375800898854</v>
+        <v>-0.7652513386432909</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.718397498076909</v>
+        <v>-2.608062336303168</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.536125201191321</v>
+        <v>1.602326298255565</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.566397753233636</v>
+        <v>-9.566086597594728</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6730121417314878</v>
+        <v>-0.6728876794759246</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.344002397980372</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.681300848023247</v>
+        <v>1.747501945087491</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.859318129728798</v>
+        <v>-8.85900697408989</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3929673259898534</v>
+        <v>-0.3928428637342902</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.454337559754113</v>
+        <v>-2.344002397980372</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.678513814362946</v>
+        <v>1.74471491142719</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.819133831362608</v>
+        <v>-8.8188226757237</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3765499827555359</v>
+        <v>-0.3764255204999727</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.414153261387922</v>
+        <v>-2.303818099614181</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.702968017270502</v>
+        <v>1.769169114334746</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.739064035824804</v>
+        <v>-8.738752880185896</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3451552433196574</v>
+        <v>-0.3450307810640942</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.334083465850118</v>
+        <v>-2.223748304076377</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.750376715813941</v>
+        <v>1.816577812878185</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505582813595204</v>
+        <v>-8.505271657956296</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.243838325589965</v>
+        <v>-0.2437138633344018</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.100602243620519</v>
+        <v>-1.990267081846779</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.898389877989553</v>
+        <v>1.964590975053797</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.35591642258769</v>
+        <v>-8.355605266948782</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1868639794999187</v>
+        <v>-0.1867395172443556</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.007698752377983</v>
+        <v>-1.897363590604243</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.951239762422115</v>
+        <v>2.017440859486359</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223640948956803</v>
+        <v>-8.223329793317895</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1385863033005368</v>
+        <v>-0.1384618410449736</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.875423278747097</v>
+        <v>-1.765088116973356</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.025972533347674</v>
+        <v>2.092173630411918</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.033041274283649</v>
+        <v>-8.032730118644741</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0595313727436384</v>
+        <v>-0.05940691048807523</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.574488442300203</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.143147398839202</v>
+        <v>2.209348495903447</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.784041475600068</v>
+        <v>-7.78373031996116</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0529748879534524</v>
+        <v>0.05309935020901557</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.684823604073944</v>
+        <v>-1.574488442300203</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.156053740062861</v>
+        <v>2.222254837127105</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889631465373173</v>
+        <v>-7.889320309734265</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1172370375550078</v>
+        <v>-0.1171125752994446</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.790413593847048</v>
+        <v>-1.680078432073308</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.96472381659978</v>
+        <v>2.030924913664024</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908366367491769</v>
+        <v>-7.908055211852862</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07618665652536016</v>
+        <v>-0.07606219426979699</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.79600960350718</v>
+        <v>-1.685674441733439</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.009910552680787</v>
+        <v>2.076111649745032</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.846496977136879</v>
+        <v>-7.760115170445262</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.171317823071572</v>
+        <v>-0.1367651003949248</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.834232881885876</v>
+        <v>-1.665353525824881</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.867097662965402</v>
+        <v>1.968425276601999</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.829338827005585</v>
+        <v>-7.742957020313968</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1731685492725323</v>
+        <v>-0.1386158265958857</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.817074731754582</v>
+        <v>-1.648195375693587</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.8686785667907</v>
+        <v>1.970006180427297</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.785790420234894</v>
+        <v>-7.699408613543278</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1627097986593493</v>
+        <v>-0.1281570759827027</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.817074731754582</v>
+        <v>-1.648195375693587</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.861717954695607</v>
+        <v>1.963045568332204</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.543642026781036</v>
+        <v>-7.457260220089419</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.05138808689666297</v>
+        <v>-0.0168353642200163</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.817074731754582</v>
+        <v>-1.648195375693587</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.87618030907675</v>
+        <v>1.977507922713347</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.435382889658515</v>
+        <v>-7.349001082966898</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.01355231158845926</v>
+        <v>0.0210004110881874</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.817074731754582</v>
+        <v>-1.648195375693587</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.870712429535945</v>
+        <v>1.972040043172542</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.312091754841384</v>
+        <v>-7.225709948149767</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03326223634896985</v>
+        <v>0.06781495902561696</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.693783596937452</v>
+        <v>-1.524904240876457</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.9421852044368</v>
+        <v>2.043512818073397</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.29094255593794</v>
+        <v>-7.204560749246324</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.04942289414767265</v>
+        <v>0.08397561682431931</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.672634398034008</v>
+        <v>-1.503755041973013</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.962575702016192</v>
+        <v>2.063903315652788</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.047177113954496</v>
+        <v>-6.960795307262879</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1427097792881011</v>
+        <v>0.1772625019647478</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.672634398034008</v>
+        <v>-1.503755041973013</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.958356410363242</v>
+        <v>2.059684023999839</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.945414293677201</v>
+        <v>-6.859032486985584</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.185539221319035</v>
+        <v>0.2200919439956817</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.659415329641579</v>
+        <v>-1.490535973580585</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.968412165318715</v>
+        <v>2.069739778955312</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.695563899728127</v>
+        <v>-6.60918209303651</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2782214538823671</v>
+        <v>0.3127741765590137</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.659415329641579</v>
+        <v>-1.490535973580585</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.961154240302418</v>
+        <v>2.062481853939014</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.519671807260695</v>
+        <v>-6.433290000569077</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3521774143899883</v>
+        <v>0.3867301370666354</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.659415329641579</v>
+        <v>-1.490535973580585</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.964753363823066</v>
+        <v>2.066080977459663</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.348225344238231</v>
+        <v>-6.261843537546613</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4340835056535277</v>
+        <v>0.4686362283301748</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.487968866619116</v>
+        <v>-1.319089510558122</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.080948747691098</v>
+        <v>2.182276361327695</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.123192344569408</v>
+        <v>-6.03681053787779</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5231171831373538</v>
+        <v>0.5576699058140009</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.262935866950293</v>
+        <v>-1.094056510889299</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.214989025108689</v>
+        <v>2.316316638745286</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.059556602335474</v>
+        <v>-5.973174795643856</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5532662810852447</v>
+        <v>0.5878190037618918</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.199300124716359</v>
+        <v>-1.030420768655364</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.257865271503367</v>
+        <v>2.359192885139963</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.966556561129575</v>
+        <v>-5.880174754437958</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5716605563513997</v>
+        <v>0.6062132790280468</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.199300124716359</v>
+        <v>-1.030420768655364</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.239059530287162</v>
+        <v>2.340387143923759</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.726126064324715</v>
+        <v>-5.639744257633097</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6695758316982214</v>
+        <v>0.7041285543748685</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9588696279114985</v>
+        <v>-0.7899902718505039</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.385060904994956</v>
+        <v>2.486388518631553</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.65388349615352</v>
+        <v>-5.567501689461903</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7024021728015195</v>
+        <v>0.7369548954781666</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9588696279114985</v>
+        <v>-0.7899902718505039</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.388990218829776</v>
+        <v>2.490317832466373</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.600885173872133</v>
+        <v>-5.514503367180515</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7242800856314147</v>
+        <v>0.7588328083080618</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9035333689095597</v>
+        <v>-0.734654012848565</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.422870558148279</v>
+        <v>2.524198171784876</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.492080288392406</v>
+        <v>-5.405698481700788</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7648001110432987</v>
+        <v>0.7993528337199458</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9035333689095597</v>
+        <v>-0.734654012848565</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.419868629368273</v>
+        <v>2.521196243004869</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.272059490355395</v>
+        <v>-5.185677683663777</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8543874672687171</v>
+        <v>0.8889401899453642</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7623135238415795</v>
+        <v>-0.5934341677805848</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.506179573419675</v>
+        <v>2.607507187056272</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.139191801292117</v>
+        <v>-5.0528099946005</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9234287256958513</v>
+        <v>0.9579814483724984</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7623135238415795</v>
+        <v>-0.5934341677805848</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.522073756221499</v>
+        <v>2.623401369858095</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.979676697772748</v>
+        <v>-4.89329489108113</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9883806115439013</v>
+        <v>1.022933334220548</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6027984203222095</v>
+        <v>-0.4339190642612148</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.618928662773422</v>
+        <v>2.720256276410019</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.83500455267301</v>
+        <v>-4.748622745981392</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.056337572145236</v>
+        <v>1.090890294821883</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4581262752224721</v>
+        <v>-0.2892469191614774</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.715820052394704</v>
+        <v>2.817147666031302</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.894879380030702</v>
+        <v>-4.808497573339085</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.018425132603585</v>
+        <v>1.052977855280232</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5180011025801643</v>
+        <v>-0.3491217465191696</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.665932647381515</v>
+        <v>2.767260261018112</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.808079882251693</v>
+        <v>-4.721698075560075</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.075545425037755</v>
+        <v>1.110098147714402</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5180011025801643</v>
+        <v>-0.3491217465191696</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.688333140704081</v>
+        <v>2.789660754340678</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.810549588713499</v>
+        <v>-4.724167782021881</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.074629943826445</v>
+        <v>1.109182666503092</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5204708090419705</v>
+        <v>-0.3515914529809757</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.68692371820041</v>
+        <v>2.788251331837007</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.87891977503751</v>
+        <v>-4.792537968345892</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.058288791771542</v>
+        <v>1.09284151444819</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5111951100057556</v>
+        <v>-0.3423157539447608</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.703496060096841</v>
+        <v>2.804823673733437</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.991414914404595</v>
+        <v>-4.898297399934482</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.0037274446566</v>
+        <v>1.040974450444645</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5111951100057556</v>
+        <v>-0.3423157539447608</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.693932768728732</v>
+        <v>2.795260382365329</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.0224080737333</v>
+        <v>-4.929290559263188</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8160397459655044</v>
+        <v>0.8532867517535494</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5111951100057556</v>
+        <v>-0.3423157539447608</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.518642333769119</v>
+        <v>2.619969947405715</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.846933813940831</v>
+        <v>-4.753816299470719</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8907966818742796</v>
+        <v>0.9280436876623246</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5111951100057556</v>
+        <v>-0.3423157539447608</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.523209565760907</v>
+        <v>2.624537179397503</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.95787006658208</v>
+        <v>-4.864752552111968</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8221642095789872</v>
+        <v>0.8594112153670321</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5111951100057556</v>
+        <v>-0.3423157539447608</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.498951594522114</v>
+        <v>2.60027920815871</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.160896644125313</v>
+        <v>-5.067779129655201</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7440849637815994</v>
+        <v>0.7813319695696443</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.714221687548989</v>
+        <v>-0.5453423314879942</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.380267033216079</v>
+        <v>2.481594646852676</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.00297104519002</v>
+        <v>-4.909853530719908</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8174275897878491</v>
+        <v>0.8546745955758939</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.714221687548989</v>
+        <v>-0.5453423314879942</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.390439419648211</v>
+        <v>2.491767033284808</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.916727582163642</v>
+        <v>-4.82361006769353</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8468712455722605</v>
+        <v>0.8841182513603054</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.714221687548989</v>
+        <v>-0.5453423314879942</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.385385690222072</v>
+        <v>2.486713303858668</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.962034401562622</v>
+        <v>-4.86891688709251</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8205242932571941</v>
+        <v>0.8577712990452389</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7550318505582198</v>
+        <v>-0.586152494497225</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.352675367861059</v>
+        <v>2.454002981497656</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.991067506264923</v>
+        <v>-4.897949991794811</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8094629244093752</v>
+        <v>0.8467099301974201</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7550318505582198</v>
+        <v>-0.586152494497225</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.353227240894161</v>
+        <v>2.454554854530757</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.898257024814064</v>
+        <v>-4.805139510343952</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7758598088810846</v>
+        <v>0.8131068146691296</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6622213691073604</v>
+        <v>-0.4933420130463656</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.338186221656041</v>
+        <v>2.439513835292638</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.942646494143491</v>
+        <v>-4.849528979673379</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7599774970739146</v>
+        <v>0.7972245028619593</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7066108384367881</v>
+        <v>-0.5377314823757933</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.313426015982986</v>
+        <v>2.414753629619582</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.829975275907241</v>
+        <v>-4.736857761437129</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8001216928801376</v>
+        <v>0.8373686986681825</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.5939396202005378</v>
+        <v>-0.4250602641395431</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.376104455436459</v>
+        <v>2.477432069073056</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.717598274724568</v>
+        <v>-4.624480760254456</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.850563789183874</v>
+        <v>0.8878107949719189</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.5939396202005378</v>
+        <v>-0.4250602641395431</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.381595751267126</v>
+        <v>2.482923364903723</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.915832843611299</v>
+        <v>-4.822715329141187</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7827671633977207</v>
+        <v>0.8200141691857656</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7921741890872684</v>
+        <v>-0.6232948330262736</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.274152211703627</v>
+        <v>2.375479825340224</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.998834124636578</v>
+        <v>-4.905716610166466</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5879223709882624</v>
+        <v>0.6251693767763074</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.8107450736144421</v>
+        <v>-0.6418657175534475</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.101365400987976</v>
+        <v>2.202693014624573</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.107448203079909</v>
+        <v>-5.014330688609797</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6646264003301354</v>
+        <v>0.7018734061181804</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.8107450736144421</v>
+        <v>-0.6418657175534475</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.221515061707182</v>
+        <v>2.322842675343778</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.194046786061012</v>
+        <v>-5.1009292715909</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6444999932400175</v>
+        <v>0.6817469990280625</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.8107450736144421</v>
+        <v>-0.6418657175534475</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.236028087809505</v>
+        <v>2.337355701446101</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.155663123502861</v>
+        <v>-5.062545609032749</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6572728996056467</v>
+        <v>0.6945199053936912</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.772361411056291</v>
+        <v>-0.6034820549952963</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.256477726686764</v>
+        <v>2.357805340323361</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.978546793467695</v>
+        <v>-4.885429278997583</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7248484604650149</v>
+        <v>0.7620954662530597</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.772361411056291</v>
+        <v>-0.6034820549952963</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.253206755532066</v>
+        <v>2.354534369168662</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.948844669491401</v>
+        <v>-4.855727155021289</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7374127018174454</v>
+        <v>0.7746597076054904</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.7768315362716043</v>
+        <v>-0.6079521802106096</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.251208072164791</v>
+        <v>2.352535685801388</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.769469248252634</v>
+        <v>-4.676351733782521</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8029498456193669</v>
+        <v>0.8401968514074118</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6200547781008856</v>
+        <v>-0.4511754220398909</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339061102373637</v>
+        <v>2.440388716010233</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.814483461773239</v>
+        <v>-4.721365947303127</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7657516155427144</v>
+        <v>0.8029986213307592</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6504036734154902</v>
+        <v>-0.4815243173544955</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.301659220516464</v>
+        <v>2.40298683415306</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.081487972045674</v>
+        <v>-4.988370457575562</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6646413737726862</v>
+        <v>0.7018883795607309</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8447667114584387</v>
+        <v>-0.675887355397444</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.19073296002964</v>
+        <v>2.292060573666237</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.182685753482847</v>
+        <v>-5.089568239012735</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6233661830943182</v>
+        <v>0.6606131888823632</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9131755250037579</v>
+        <v>-0.7442961689427632</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.14889159379895</v>
+        <v>2.250219207435547</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.150210167312075</v>
+        <v>-5.057092652841963</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.633956379116944</v>
+        <v>0.671203384904989</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9131755250037579</v>
+        <v>-0.7442961689427632</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.146491555353267</v>
+        <v>2.247819168989864</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.131172039604778</v>
+        <v>-5.038054525134665</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6380963494081078</v>
+        <v>0.6753433551961527</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9713591363349524</v>
+        <v>-0.8024797802739577</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108106107762795</v>
+        <v>2.209433721399392</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.162298670755396</v>
+        <v>-5.069181156285284</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8032275658865409</v>
+        <v>0.8404745716745858</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9713591363349524</v>
+        <v>-0.8024797802739577</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.285687976701475</v>
+        <v>2.387015590338073</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.214619051356188</v>
+        <v>-5.121501536886075</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.783132742632358</v>
+        <v>0.820379748420403</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9364122763260803</v>
+        <v>-0.7675329202650856</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.307489421692932</v>
+        <v>2.408817035329529</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.234876349885146</v>
+        <v>-5.141758835415033</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7810383536177006</v>
+        <v>0.8182853594057455</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9364122763260803</v>
+        <v>-0.7675329202650856</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.313497952089858</v>
+        <v>2.414825565726455</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.087133379650143</v>
+        <v>-4.994015865180031</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9192881895037237</v>
+        <v>0.9565351952917684</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7686049190911971</v>
+        <v>-0.5997255630302024</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.49333501422281</v>
+        <v>2.594662627859407</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.189148062181364</v>
+        <v>-5.096030547711252</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.881275938022716</v>
+        <v>0.9185229438107609</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7686049190911971</v>
+        <v>-0.5997255630302024</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496128635754291</v>
+        <v>2.597456249390888</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.052538718087272</v>
+        <v>-4.959421203617159</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9365820240520115</v>
+        <v>0.9738290298400565</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6319955749971047</v>
+        <v>-0.4631162189361099</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.578756590602405</v>
+        <v>2.680084204239002</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.195304050909922</v>
+        <v>-5.10218653643981</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8785563676630619</v>
+        <v>0.9158033734511064</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.774760907819755</v>
+        <v>-0.6058815517587604</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.492177867648925</v>
+        <v>2.593505481285522</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.133006052133799</v>
+        <v>-5.039888537663687</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9698111209703315</v>
+        <v>1.007058126758376</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.774760907819755</v>
+        <v>-0.6058815517587604</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.558513421445746</v>
+        <v>2.659841035082342</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.931215854468642</v>
+        <v>-5.037709954806019</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7591080724257928</v>
+        <v>0.7165104322908418</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.5767427156506006</v>
+        <v>-0.6135276879566587</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.385905209136637</v>
+        <v>2.363834225753002</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.871325172826048</v>
+        <v>-4.977819273163425</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8533545774050053</v>
+        <v>0.8107569372700545</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5168520340080072</v>
+        <v>-0.5536370063140652</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.492129850444368</v>
+        <v>2.470058867060733</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.969065717451023</v>
+        <v>-5.0755598177884</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8288860956710591</v>
+        <v>0.7862884555361083</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5327413121409874</v>
+        <v>-0.5695262844470454</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.497224019680623</v>
+        <v>2.475153036296988</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.145403477573952</v>
+        <v>-5.251897577911329</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.756886972446559</v>
+        <v>0.7142893323116084</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7090790722639169</v>
+        <v>-0.7458640445699749</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.389957344431537</v>
+        <v>2.367886361047903</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.144714105412729</v>
+        <v>-5.251208205750106</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7556543393509769</v>
+        <v>0.7130566992160259</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7090790722639169</v>
+        <v>-0.7458640445699749</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.388448962471466</v>
+        <v>2.366377979087831</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.151285070467321</v>
+        <v>-5.257779170804699</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7528888207645759</v>
+        <v>0.7102911806296253</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7156500373185097</v>
+        <v>-0.7524350096245678</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.384369250874146</v>
+        <v>2.362298267490512</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.143331100172549</v>
+        <v>-5.249825200509926</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.756070408882485</v>
+        <v>0.713472768747534</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7156500373185097</v>
+        <v>-0.7524350096245678</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.384369250874146</v>
+        <v>2.362298267490512</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.132957723839462</v>
+        <v>-5.23945182417684</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7666015164435245</v>
+        <v>0.7240038763085734</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7052766609854224</v>
+        <v>-0.7420616332914804</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.396975033701803</v>
+        <v>2.374904050318169</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.005273414045166</v>
+        <v>-5.111767514382543</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8225676137359677</v>
+        <v>0.7799699736010166</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.577592351191126</v>
+        <v>-0.614377323497184</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.478477992953106</v>
+        <v>2.456407009569471</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.065940004447555</v>
+        <v>-5.172434104784932</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7850556500508845</v>
+        <v>0.7424580099159335</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6592906679096596</v>
+        <v>-0.6960756402157177</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.416213675397858</v>
+        <v>2.394142692014223</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.000946144513909</v>
+        <v>-5.107440244851286</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8151508966349712</v>
+        <v>0.7725532565000202</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6324600533055043</v>
+        <v>-0.6692450256115623</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.43640974677098</v>
+        <v>2.414338763387345</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.101704780270907</v>
+        <v>-5.208198880608284</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7790083819632501</v>
+        <v>0.736410741828299</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7212856220325097</v>
+        <v>-0.7580705943385677</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.387275345165855</v>
+        <v>2.36520436178222</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.057501943185007</v>
+        <v>-5.163996043522384</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8025691193254474</v>
+        <v>0.7599714791904963</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6770827849466092</v>
+        <v>-0.7138677572526673</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.419676649945232</v>
+        <v>2.397605666561597</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.09448097084845</v>
+        <v>-5.200975071185827</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7861875087293178</v>
+        <v>0.7435898685943667</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6401088831552787</v>
+        <v>-0.6768938554613367</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.440270991489278</v>
+        <v>2.418200008105643</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042144</v>
+        <v>3.863924114042142</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.11453904971329</v>
+        <v>-5.221033150050667</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8294120423664211</v>
+        <v>0.7868144022314705</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6401088831552787</v>
+        <v>-0.6768938554613367</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.491518756672318</v>
+        <v>2.469447773288683</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.844986470221169</v>
+        <v>3.737629461003941</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.864629961470227</v>
+        <v>2.631832191941115</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.11453904971329</v>
+        <v>-5.221033150050667</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8294120423664211</v>
+        <v>0.7868144022314705</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.6401088831552787</v>
+        <v>-0.6768938554613367</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.857693758456595</v>
+        <v>2.624895988927483</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.7%</t>
+          <t>-679.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-163.8%</t>
+          <t>466.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-297.5%</t>
+          <t>-296.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-295.1%</t>
+          <t>-306.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.3%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-297.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-177.4%</t>
+          <t>-184.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.5%</t>
+          <t>-183.1%</t>
         </is>
       </c>
     </row>
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.117349142183405</v>
+        <v>-4.117660297822314</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.492563580019753</v>
+        <v>1.492439117764189</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3743635145062945</v>
+        <v>-0.484698676280035</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.915241552503085</v>
+        <v>2.849040455438841</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.323860919070427</v>
+        <v>-4.324172074709336</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.406064927921202</v>
+        <v>1.405940465665638</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.580875291393316</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.787440545027131</v>
+        <v>2.721239447962886</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.579702004849119</v>
+        <v>-4.580013160488028</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.305501420309984</v>
+        <v>1.305376958054421</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.580875291393316</v>
+        <v>-0.6912104531670565</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.78921347172739</v>
+        <v>2.723012374663146</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.011507797998907</v>
+        <v>-5.011818953637816</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.119111990517474</v>
+        <v>1.11898752826191</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7172927878345829</v>
+        <v>-0.8276279496083235</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.693695861330034</v>
+        <v>2.62749476426579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.246201792131459</v>
+        <v>-5.246512947770368</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.013519167866543</v>
+        <v>1.01339470561098</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7109565206053278</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.685782396669678</v>
+        <v>2.619581299605434</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.581864439361912</v>
+        <v>-5.582175595000821</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8778347006303275</v>
+        <v>0.8777102383747644</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7109565206053278</v>
+        <v>-0.8212916823790684</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.684362988325643</v>
+        <v>2.618161891261399</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.945490684262225</v>
+        <v>-5.945801839901134</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7388717629044441</v>
+        <v>0.7387473006488805</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8091781574724536</v>
+        <v>-0.9195133192461942</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.63191756643961</v>
+        <v>2.565716469375365</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.310618066900972</v>
+        <v>-6.310929222539881</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5920753248547768</v>
+        <v>0.5919508625992131</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.105488941771466</v>
+        <v>-1.215824103545207</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.453385610866033</v>
+        <v>2.387184513801789</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.719206844081651</v>
+        <v>-6.719517999720559</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.427401357997264</v>
+        <v>0.4272768957417008</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.206993888572385</v>
+        <v>2.140792791508141</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.995782944397483</v>
+        <v>-6.996094100036391</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3119563503423919</v>
+        <v>0.3118318880868287</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.202179321043846</v>
+        <v>2.135978223979602</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.41217481868448</v>
+        <v>-7.412485974323388</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1433936512364702</v>
+        <v>0.143269188980907</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.200173371652723</v>
+        <v>2.133972274588479</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.728786761225129</v>
+        <v>-7.729097916864037</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.02700756488888967</v>
+        <v>0.02688310263332649</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.210432062321402</v>
+        <v>2.144230965257158</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.074661583209938</v>
+        <v>-8.074972738848846</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1152427987593385</v>
+        <v>-0.1153672610149017</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.206531627467097</v>
+        <v>2.140330530402853</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.238241461394322</v>
+        <v>-8.23855261703323</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1822698299780914</v>
+        <v>-0.1823942922336546</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.514077718952145</v>
+        <v>-1.624412880725885</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.204936547522098</v>
+        <v>2.138735450457854</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.53490280320452</v>
+        <v>-8.535213958843428</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2971553907729625</v>
+        <v>-0.2972798530285257</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.582820854686023</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.167469642010979</v>
+        <v>2.101268544946735</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.739933983978837</v>
+        <v>-8.740245139617745</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3831941676170922</v>
+        <v>-0.3833186298726554</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.582820854686023</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.163443337476576</v>
+        <v>2.097242240412332</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.122935372721468</v>
+        <v>-9.123246528360376</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5364968244357287</v>
+        <v>-0.5366212866912918</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.582820854686023</v>
+        <v>-1.693156016459764</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.163341236154992</v>
+        <v>2.097140139090748</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.304805163706503</v>
+        <v>-9.305116319345411</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6066732248583127</v>
+        <v>-0.6067976871138758</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.764690645671058</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.056790877535401</v>
+        <v>1.990589780471157</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.664335486210504</v>
+        <v>-9.664646641849412</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.745135050561863</v>
+        <v>-0.7452595128174262</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.764690645671058</v>
+        <v>-1.875025807444799</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.062141180833452</v>
+        <v>1.995940083769207</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.714684549664726</v>
+        <v>-9.714995705303634</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7573586559863741</v>
+        <v>-0.7574831182419373</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.81503970912528</v>
+        <v>-1.925374870899021</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.039847762718096</v>
+        <v>1.973646665653852</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.812303827086122</v>
+        <v>-9.81261498272503</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.793364616333164</v>
+        <v>-0.7934890785887272</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.912658986546677</v>
+        <v>-2.022994148320417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.984317946887026</v>
+        <v>1.918116849822782</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.959829915091765</v>
+        <v>-9.960141070730673</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.849481495213849</v>
+        <v>-0.8496059574694121</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.06018507455232</v>
+        <v>-2.170520236326061</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.898695850405213</v>
+        <v>1.832494753340968</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.16408809042163</v>
+        <v>-10.16439924606054</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9256715682271519</v>
+        <v>-0.9257960304827151</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.187824019166309</v>
+        <v>-2.29815918094005</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.827625680755462</v>
+        <v>1.761424583691217</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729894</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.30589786462842</v>
+        <v>-10.30620902026732</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9779129234254307</v>
+        <v>-0.9780373856809939</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.359102816811885</v>
+        <v>-2.469437978585626</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.729340956652552</v>
+        <v>1.663139859588308</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440637</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.23242803296097</v>
+        <v>-10.23273918859988</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9331532892650305</v>
+        <v>-0.9332777515205937</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.285632985144436</v>
+        <v>-2.395968146918177</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.788794557146443</v>
+        <v>1.722593460082198</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608603</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.40755245034751</v>
+        <v>-10.40786360598642</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9886478354721309</v>
+        <v>-0.988772297727694</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.46075740253098</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.698275127462033</v>
+        <v>1.632074030397789</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.642004544362</v>
+        <v>-10.64231570000091</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.089647837979523</v>
+        <v>-1.089772300235086</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.46075740253098</v>
+        <v>-2.571092564304721</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.691055962560437</v>
+        <v>1.624854865496193</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.92980838889924</v>
+        <v>-10.93011954453815</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.211441566568394</v>
+        <v>-1.211566028823957</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.748561247068218</v>
+        <v>-2.858896408841959</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.511701465064118</v>
+        <v>1.445500367999874</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390588</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.98259454449957</v>
+        <v>-10.98290570013847</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.231440238969968</v>
+        <v>-1.231564701225532</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.844236733650615</v>
+        <v>-2.954571895424356</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.455411962953236</v>
+        <v>1.389210865888992</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297402</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.10863133786786</v>
+        <v>-11.10894249350676</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.279161227688169</v>
+        <v>-1.279285689943733</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.818985110840873</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.473256665268196</v>
+        <v>1.407055568203952</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.05661582389904</v>
+        <v>-11.05692697953795</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.254364686414243</v>
+        <v>-1.254489148669807</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.818985110840873</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.477247000954597</v>
+        <v>1.411045903890353</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158925</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.19828766562316</v>
+        <v>-11.19859882126207</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.312508650002633</v>
+        <v>-1.312633112258196</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.818985110840873</v>
+        <v>-2.929320272614614</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.475771774055855</v>
+        <v>1.409570676991611</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940723</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.14869682119833</v>
+        <v>-11.14900797683724</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.277618902067827</v>
+        <v>-1.277743364323391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.769394266416039</v>
+        <v>-2.87972942818978</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.520579690875628</v>
+        <v>1.454378593811384</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.13588942819355</v>
+        <v>-11.13620058383246</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285547078512601</v>
+        <v>-1.285671540768164</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81825004142494</v>
+        <v>-2.928585203198681</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.478215092223604</v>
+        <v>1.41201399515936</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91004427547414</v>
+        <v>-10.91035543111305</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185629944388628</v>
+        <v>-1.185754406644191</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.776323365837777</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.512950170612111</v>
+        <v>1.446749073547867</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78546561913655</v>
+        <v>-10.78577677477546</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134659337297532</v>
+        <v>-1.134783799553095</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.776323365837777</v>
+        <v>-2.886658527611517</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51408931516817</v>
+        <v>1.447888218103926</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646222</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83836090718084</v>
+        <v>-10.77881529651684</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.153183678353138</v>
+        <v>-1.12936543408754</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.77136801974933</v>
+        <v>-2.814861637417943</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.519696296983345</v>
+        <v>1.493600126382178</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611573</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.55445217625209</v>
+        <v>-10.49490656558809</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.033886481743003</v>
+        <v>-1.010068237477403</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.77136801974933</v>
+        <v>-2.814861637417943</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.525430001221982</v>
+        <v>1.499333830620814</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48308578364244</v>
+        <v>-10.42354017297844</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.015077187093009</v>
+        <v>-0.9912589428274101</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.700001627139682</v>
+        <v>-2.743495244808295</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.558512574393906</v>
+        <v>1.532416403792738</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21924891643837</v>
+        <v>-10.15970330577437</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9194259215242888</v>
+        <v>-0.8956076772586896</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.700001627139682</v>
+        <v>-2.743495244808295</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.548629093080998</v>
+        <v>1.52253292247983</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.952007115569973</v>
+        <v>-9.892461504905976</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8143637616763031</v>
+        <v>-0.7905455174107043</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.700001627139682</v>
+        <v>-2.743495244808295</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.546794532581624</v>
+        <v>1.520698361980457</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311951</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.854100076893483</v>
+        <v>-9.794554466229485</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7755012611791678</v>
+        <v>-0.7516830169135686</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.632015877279126</v>
+        <v>-2.675509494947739</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.587285667524497</v>
+        <v>1.56118949692333</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.830146535917525</v>
+        <v>-9.770600925253527</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7652513386432909</v>
+        <v>-0.7414330943776921</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.608062336303168</v>
+        <v>-2.651555953971781</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.602326298255565</v>
+        <v>1.576230127654398</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.566086597594728</v>
+        <v>-9.50654098693073</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6728876794759246</v>
+        <v>-0.6490694352103255</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.344002397980372</v>
+        <v>-2.387496015648985</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.747501945087491</v>
+        <v>1.721405774486323</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.85900697408989</v>
+        <v>-8.799461363425893</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3928428637342902</v>
+        <v>-0.3690246194686915</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.344002397980372</v>
+        <v>-2.387496015648985</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.74471491142719</v>
+        <v>1.718618740826022</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.8188226757237</v>
+        <v>-8.759277065059702</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3764255204999727</v>
+        <v>-0.3526072762343739</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.303818099614181</v>
+        <v>-2.347311717282794</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.769169114334746</v>
+        <v>1.743072943733578</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.738752880185896</v>
+        <v>-8.679207269521898</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3450307810640942</v>
+        <v>-0.321212536798495</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.223748304076377</v>
+        <v>-2.26724192174499</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.816577812878185</v>
+        <v>1.790481642277018</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291816</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.505271657956296</v>
+        <v>-8.4457260472923</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2437138633344018</v>
+        <v>-0.2198956190688035</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.990267081846779</v>
+        <v>-2.033760699515392</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.964590975053797</v>
+        <v>1.938494804452629</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.355605266948782</v>
+        <v>-8.296059656284786</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1867395172443556</v>
+        <v>-0.1629212729787572</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.897363590604243</v>
+        <v>-1.940857208272856</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.017440859486359</v>
+        <v>1.991344688885191</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.223329793317895</v>
+        <v>-8.163784182653899</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1384618410449736</v>
+        <v>-0.1146435967793753</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.765088116973356</v>
+        <v>-1.808581734641969</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.092173630411918</v>
+        <v>2.06607745981075</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105958</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.032730118644741</v>
+        <v>-7.973184507980746</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.05940691048807523</v>
+        <v>-0.03558866622247736</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.574488442300203</v>
+        <v>-1.617982059968816</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.209348495903447</v>
+        <v>2.183252325302279</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.78373031996116</v>
+        <v>-7.724184709297165</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05309935020901557</v>
+        <v>0.07691759447461388</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.574488442300203</v>
+        <v>-1.617982059968816</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.222254837127105</v>
+        <v>2.196158666525938</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.889320309734265</v>
+        <v>-7.82977469907027</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1171125752994446</v>
+        <v>-0.09329433103384677</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.680078432073308</v>
+        <v>-1.723572049741921</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.030924913664024</v>
+        <v>2.004828743062856</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987909</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.908055211852862</v>
+        <v>-7.848509601188867</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07606219426979699</v>
+        <v>-0.05224395000419912</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.685674441733439</v>
+        <v>-1.729168059402052</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.076111649745032</v>
+        <v>2.050015479143864</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.760115170445262</v>
+        <v>-7.700569559781267</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1367651003949248</v>
+        <v>-0.112946856129327</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.665353525824881</v>
+        <v>-1.708847143493494</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.968425276601999</v>
+        <v>1.942329106000831</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409212</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.742957020313968</v>
+        <v>-7.683411409649973</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1386158265958857</v>
+        <v>-0.1147975823302874</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.648195375693587</v>
+        <v>-1.6916889933622</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.970006180427297</v>
+        <v>1.943910009826129</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098116</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.699408613543278</v>
+        <v>-7.639863002879283</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1281570759827027</v>
+        <v>-0.1043388317171043</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.648195375693587</v>
+        <v>-1.6916889933622</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.963045568332204</v>
+        <v>1.936949397731036</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.457260220089419</v>
+        <v>-7.397714609425424</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.0168353642200163</v>
+        <v>0.006982880045582007</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.648195375693587</v>
+        <v>-1.6916889933622</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.977507922713347</v>
+        <v>1.951411752112179</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722823</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.349001082966898</v>
+        <v>-7.289455472302903</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0210004110881874</v>
+        <v>0.04481865535378571</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.648195375693587</v>
+        <v>-1.6916889933622</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.972040043172542</v>
+        <v>1.945943872571374</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792053</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.225709948149767</v>
+        <v>-7.166164337485772</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06781495902561696</v>
+        <v>0.09163320329121483</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.524904240876457</v>
+        <v>-1.56839785854507</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.043512818073397</v>
+        <v>2.017416647472229</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919914</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.204560749246324</v>
+        <v>-7.145015138582329</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08397561682431931</v>
+        <v>0.1077938610899172</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.503755041973013</v>
+        <v>-1.547248659641626</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.063903315652788</v>
+        <v>2.03780714505162</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318099</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.960795307262879</v>
+        <v>-6.901249696598884</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1772625019647478</v>
+        <v>0.2010807462303457</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.503755041973013</v>
+        <v>-1.547248659641626</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.059684023999839</v>
+        <v>2.033587853398671</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057532</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.859032486985584</v>
+        <v>-6.799486876321589</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2200919439956817</v>
+        <v>0.2439101882612795</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.490535973580585</v>
+        <v>-1.534029591249198</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.069739778955312</v>
+        <v>2.043643608354144</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279192</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.60918209303651</v>
+        <v>-6.549636482372515</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3127741765590137</v>
+        <v>0.3365924208246116</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.490535973580585</v>
+        <v>-1.534029591249198</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.062481853939014</v>
+        <v>2.036385683337847</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011505</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.433290000569077</v>
+        <v>-6.373744389905083</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3867301370666354</v>
+        <v>0.4105483813322333</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.490535973580585</v>
+        <v>-1.534029591249198</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.066080977459663</v>
+        <v>2.039984806858495</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392994</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.261843537546613</v>
+        <v>-6.202297926882619</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4686362283301748</v>
+        <v>0.4924544725957722</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.319089510558122</v>
+        <v>-1.362583128226734</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.182276361327695</v>
+        <v>2.156180190726527</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632789</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.03681053787779</v>
+        <v>-6.194752954940125</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5576699058140009</v>
+        <v>0.4944929389890671</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.094056510889299</v>
+        <v>-1.35503815628424</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.316316638745286</v>
+        <v>2.15972765150832</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.973174795643856</v>
+        <v>-6.13111721270619</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5878190037618918</v>
+        <v>0.524642036936958</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.030420768655364</v>
+        <v>-1.291402414050305</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.359192885139963</v>
+        <v>2.202603897902999</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.880174754437958</v>
+        <v>-6.038117171500292</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6062132790280468</v>
+        <v>0.543036312203113</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.030420768655364</v>
+        <v>-1.291402414050305</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.340387143923759</v>
+        <v>2.183798156686795</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242299</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.639744257633097</v>
+        <v>-5.797686674695432</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7041285543748685</v>
+        <v>0.6409515875499348</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7899902718505039</v>
+        <v>-1.050971917245445</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.486388518631553</v>
+        <v>2.329799531394588</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367689</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.567501689461903</v>
+        <v>-5.725444106524237</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7369548954781666</v>
+        <v>0.6737779286532328</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7899902718505039</v>
+        <v>-1.050971917245445</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.490317832466373</v>
+        <v>2.333728845229408</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.514503367180515</v>
+        <v>-5.672445784242849</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7588328083080618</v>
+        <v>0.695655841483128</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.734654012848565</v>
+        <v>-0.9956356582435062</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.524198171784876</v>
+        <v>2.367609184547911</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.405698481700788</v>
+        <v>-5.563640898763122</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7993528337199458</v>
+        <v>0.736175866895012</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.734654012848565</v>
+        <v>-0.9956356582435062</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.521196243004869</v>
+        <v>2.364607255767905</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675944</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.185677683663777</v>
+        <v>-5.343620100726111</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8889401899453642</v>
+        <v>0.8257632231204304</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5934341677805848</v>
+        <v>-0.854415813175526</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.607507187056272</v>
+        <v>2.450918199819307</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.0528099946005</v>
+        <v>-5.210752411662834</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9579814483724984</v>
+        <v>0.8948044815475651</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5934341677805848</v>
+        <v>-0.854415813175526</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.623401369858095</v>
+        <v>2.46681238262113</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496268</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.89329489108113</v>
+        <v>-5.051237308143464</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.022933334220548</v>
+        <v>0.9597563673956149</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4339190642612148</v>
+        <v>-0.694900709656156</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.720256276410019</v>
+        <v>2.563667289173054</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577005</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.748622745981392</v>
+        <v>-4.906565163043727</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.090890294821883</v>
+        <v>1.027713327996949</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2892469191614774</v>
+        <v>-0.5502285645564187</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.817147666031302</v>
+        <v>2.660558678794337</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.73583922294211</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.808497573339085</v>
+        <v>-4.966439990401419</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.052977855280232</v>
+        <v>0.9898008884552985</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3491217465191696</v>
+        <v>-0.6101033919141108</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.767260261018112</v>
+        <v>2.610671273781147</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674522</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.721698075560075</v>
+        <v>-4.879640492622411</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.110098147714402</v>
+        <v>1.046921180889468</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3491217465191696</v>
+        <v>-0.6101033919141108</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.789660754340678</v>
+        <v>2.633071767103713</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430701</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.724167782021881</v>
+        <v>-4.882110199084217</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.109182666503092</v>
+        <v>1.046005699678158</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3515914529809757</v>
+        <v>-0.612573098375917</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.788251331837007</v>
+        <v>2.631662344600042</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003609</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.792537968345892</v>
+        <v>-4.950480385408227</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.09284151444819</v>
+        <v>1.029664547623256</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3423157539447608</v>
+        <v>-0.6032973993397021</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.804823673733437</v>
+        <v>2.648234686496473</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508378</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.898297399934482</v>
+        <v>-5.059018566324361</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.040974450444645</v>
+        <v>0.9766859838886934</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3423157539447608</v>
+        <v>-0.6032973993397021</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.795260382365329</v>
+        <v>2.638671395128364</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.929290559263188</v>
+        <v>-5.090011725653066</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8532867517535494</v>
+        <v>0.7889982851975978</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3423157539447608</v>
+        <v>-0.6032973993397021</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.619969947405715</v>
+        <v>2.463380960168751</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.753816299470719</v>
+        <v>-4.914537465860597</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9280436876623246</v>
+        <v>0.8637552211063733</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3423157539447608</v>
+        <v>-0.6032973993397021</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.624537179397503</v>
+        <v>2.467948192160538</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.864752552111968</v>
+        <v>-5.025473718501846</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8594112153670321</v>
+        <v>0.7951227488110808</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3423157539447608</v>
+        <v>-0.6032973993397021</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.60027920815871</v>
+        <v>2.443690220921745</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111302</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.067779129655201</v>
+        <v>-5.228500296045079</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7813319695696443</v>
+        <v>0.7170435030136928</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5453423314879942</v>
+        <v>-0.8063239768829354</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.481594646852676</v>
+        <v>2.325005659615711</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.909853530719908</v>
+        <v>-5.070574697109786</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8546745955758939</v>
+        <v>0.7903861290199425</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5453423314879942</v>
+        <v>-0.8063239768829354</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.491767033284808</v>
+        <v>2.335178046047843</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742307</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.82361006769353</v>
+        <v>-4.984331234083409</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8841182513603054</v>
+        <v>0.8198297848043539</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5453423314879942</v>
+        <v>-0.8063239768829354</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.486713303858668</v>
+        <v>2.330124316621704</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316054</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.86891688709251</v>
+        <v>-5.029638053482389</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8577712990452389</v>
+        <v>0.7934828324892877</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.586152494497225</v>
+        <v>-0.8471341398921662</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.454002981497656</v>
+        <v>2.297413994260691</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803199</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.897949991794811</v>
+        <v>-5.05867115818469</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8467099301974201</v>
+        <v>0.7824214636414686</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.586152494497225</v>
+        <v>-0.8471341398921662</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.454554854530757</v>
+        <v>2.297965867293792</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.805139510343952</v>
+        <v>-4.96586067673383</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8131068146691296</v>
+        <v>0.7488183481131783</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4933420130463656</v>
+        <v>-0.7543236584413069</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.439513835292638</v>
+        <v>2.282924848055674</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560433</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.849528979673379</v>
+        <v>-5.010250146063258</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7972245028619593</v>
+        <v>0.732936036306008</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5377314823757933</v>
+        <v>-0.7987131277707346</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.414753629619582</v>
+        <v>2.258164642382618</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.736857761437129</v>
+        <v>-4.897578927827007</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8373686986681825</v>
+        <v>0.773080232112231</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4250602641395431</v>
+        <v>-0.6860419095344843</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.477432069073056</v>
+        <v>2.320843081836091</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.624480760254456</v>
+        <v>-4.785201926644334</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8878107949719189</v>
+        <v>0.8235223284159674</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4250602641395431</v>
+        <v>-0.6860419095344843</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.482923364903723</v>
+        <v>2.326334377666758</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.822715329141187</v>
+        <v>-4.983436495531065</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8200141691857656</v>
+        <v>0.7557257026298143</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6232948330262736</v>
+        <v>-0.8842764784212149</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.375479825340224</v>
+        <v>2.218890838103259</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.905716610166466</v>
+        <v>-5.066437776556344</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6251693767763074</v>
+        <v>0.560880910220356</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6418657175534475</v>
+        <v>-0.9028473629483886</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.202693014624573</v>
+        <v>2.046104027387608</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729277</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.014330688609797</v>
+        <v>-5.175051854999675</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7018734061181804</v>
+        <v>0.6375849395622293</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6418657175534475</v>
+        <v>-0.9028473629483886</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.322842675343778</v>
+        <v>2.166253688106814</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190776</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.1009292715909</v>
+        <v>-5.261650437980778</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6817469990280625</v>
+        <v>0.6174585324721109</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6418657175534475</v>
+        <v>-0.9028473629483886</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.337355701446101</v>
+        <v>2.180766714209136</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.062545609032749</v>
+        <v>-5.223266775422627</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6945199053936912</v>
+        <v>0.6302314388377401</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6034820549952963</v>
+        <v>-0.8644637003902375</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.357805340323361</v>
+        <v>2.201216353086396</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532491</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.885429278997583</v>
+        <v>-5.046150445387461</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7620954662530597</v>
+        <v>0.6978069996971086</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6034820549952963</v>
+        <v>-0.8644637003902375</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.354534369168662</v>
+        <v>2.197945381931698</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793908</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.855727155021289</v>
+        <v>-5.016448321411167</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7746597076054904</v>
+        <v>0.7103712410495389</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6079521802106096</v>
+        <v>-0.8689338256055508</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.352535685801388</v>
+        <v>2.195946698564423</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011241</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.676351733782521</v>
+        <v>-4.8370729001724</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8401968514074118</v>
+        <v>0.7759083848514603</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4511754220398909</v>
+        <v>-0.7121570674348321</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.440388716010233</v>
+        <v>2.283799728773269</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.721365947303127</v>
+        <v>-4.882087113693006</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8029986213307592</v>
+        <v>0.7387101547748078</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4815243173544955</v>
+        <v>-0.7425059627494367</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.40298683415306</v>
+        <v>2.246397846916095</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.988370457575562</v>
+        <v>-5.149091623965441</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7018883795607309</v>
+        <v>0.6375999130047796</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.675887355397444</v>
+        <v>-0.9368690007923852</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.292060573666237</v>
+        <v>2.135471586429272</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.089568239012735</v>
+        <v>-5.250289405402613</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6606131888823632</v>
+        <v>0.5963247223264121</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7442961689427632</v>
+        <v>-1.005277814337704</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.250219207435547</v>
+        <v>2.093630220198582</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815463</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.057092652841963</v>
+        <v>-5.217813819231841</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.671203384904989</v>
+        <v>0.6069149183490374</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.7442961689427632</v>
+        <v>-1.005277814337704</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.247819168989864</v>
+        <v>2.091230181752899</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.038054525134665</v>
+        <v>-5.198775691524544</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6753433551961527</v>
+        <v>0.6110548886402012</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.8024797802739577</v>
+        <v>-1.063461425668899</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.209433721399392</v>
+        <v>2.052844734162427</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131258</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.069181156285284</v>
+        <v>-5.229902322675162</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8404745716745858</v>
+        <v>0.7761861051186347</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.8024797802739577</v>
+        <v>-1.063461425668899</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.387015590338073</v>
+        <v>2.230426603101108</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.121501536886075</v>
+        <v>-5.282222703275954</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.820379748420403</v>
+        <v>0.7560912818644514</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7675329202650856</v>
+        <v>-1.028514565660027</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.408817035329529</v>
+        <v>2.252228048092564</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.141758835415033</v>
+        <v>-5.302480001804912</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8182853594057455</v>
+        <v>0.753996892849794</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7675329202650856</v>
+        <v>-1.028514565660027</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.414825565726455</v>
+        <v>2.25823657848949</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.994015865180031</v>
+        <v>-5.154737031569909</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9565351952917684</v>
+        <v>0.8922467287358171</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5997255630302024</v>
+        <v>-0.8607072084251436</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.594662627859407</v>
+        <v>2.438073640622442</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.096030547711252</v>
+        <v>-5.256751714101131</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9185229438107609</v>
+        <v>0.8542344772548094</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5997255630302024</v>
+        <v>-0.8607072084251436</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.597456249390888</v>
+        <v>2.440867262153923</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394736</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.959421203617159</v>
+        <v>-5.120142370007038</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9738290298400565</v>
+        <v>0.9095405632841049</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4631162189361099</v>
+        <v>-0.7240978643310512</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.680084204239002</v>
+        <v>2.523495217002037</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.10218653643981</v>
+        <v>-5.262907702829688</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9158033734511064</v>
+        <v>0.8515149068951553</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.6058815517587604</v>
+        <v>-0.8668631971537015</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.593505481285522</v>
+        <v>2.436916494048557</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.039888537663687</v>
+        <v>-5.200609704053566</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.007058126758376</v>
+        <v>0.9427696602024249</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.6058815517587604</v>
+        <v>-0.8668631971537015</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.659841035082342</v>
+        <v>2.503252047845378</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.037709954806019</v>
+        <v>-4.998819506388408</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7165104322908418</v>
+        <v>0.7320666116578862</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.6135276879566587</v>
+        <v>-0.6688450049845471</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.363834225753002</v>
+        <v>2.330643835536268</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.977819273163425</v>
+        <v>-4.938928824745815</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8107569372700545</v>
+        <v>0.8263131166370987</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5536370063140652</v>
+        <v>-0.6089543233419537</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.470058867060733</v>
+        <v>2.436868476844</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.0755598177884</v>
+        <v>-5.036669369370789</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7862884555361083</v>
+        <v>0.8018446349031527</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5695262844470454</v>
+        <v>-0.6248436014749339</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.475153036296988</v>
+        <v>2.441962646080255</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.251897577911329</v>
+        <v>-5.213007129493718</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7142893323116084</v>
+        <v>0.7298455116786524</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7458640445699749</v>
+        <v>-0.8011813615978634</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.367886361047903</v>
+        <v>2.334695970831169</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.251208205750106</v>
+        <v>-5.212317757332495</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7130566992160259</v>
+        <v>0.7286128785830703</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7458640445699749</v>
+        <v>-0.8011813615978634</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.366377979087831</v>
+        <v>2.333187588871098</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.257779170804699</v>
+        <v>-5.218888722387088</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7102911806296253</v>
+        <v>0.7258473599966697</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7524350096245678</v>
+        <v>-0.8077523266524562</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.362298267490512</v>
+        <v>2.329107877273779</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863231</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.249825200509926</v>
+        <v>-5.210934752092315</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.713472768747534</v>
+        <v>0.7290289481145784</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7524350096245678</v>
+        <v>-0.8077523266524562</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.362298267490512</v>
+        <v>2.329107877273779</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.83304018194759</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.23945182417684</v>
+        <v>-5.200561375759229</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7240038763085734</v>
+        <v>0.7395600556756179</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7420616332914804</v>
+        <v>-0.7973789503193689</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.374904050318169</v>
+        <v>2.341713660101435</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326883</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.111767514382543</v>
+        <v>-5.072877065964932</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7799699736010166</v>
+        <v>0.7955261529680611</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.614377323497184</v>
+        <v>-0.6696946405250724</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.456407009569471</v>
+        <v>2.423216619352738</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314558</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.172434104784932</v>
+        <v>-5.133543656367321</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7424580099159335</v>
+        <v>0.7580141892829779</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.6960756402157177</v>
+        <v>-0.7513929572436061</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.394142692014223</v>
+        <v>2.36095230179749</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690033</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.107440244851286</v>
+        <v>-5.068549796433675</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7725532565000202</v>
+        <v>0.7881094358670646</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6692450256115623</v>
+        <v>-0.7245623426394507</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.414338763387345</v>
+        <v>2.381148373170612</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674316</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.208198880608284</v>
+        <v>-5.169308432190673</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.736410741828299</v>
+        <v>0.7519669211953435</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7580705943385677</v>
+        <v>-0.8133879113664562</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.36520436178222</v>
+        <v>2.332013971565487</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163225</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.163996043522384</v>
+        <v>-5.125105595104773</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7599714791904963</v>
+        <v>0.7755276585575408</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.7138677572526673</v>
+        <v>-0.7691850742805557</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.397605666561597</v>
+        <v>2.364415276344864</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.200975071185827</v>
+        <v>-5.162084622768216</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7435898685943667</v>
+        <v>0.7591460479614112</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6768938554613367</v>
+        <v>-0.7322111724892252</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.418200008105643</v>
+        <v>2.38500961788891</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042142</v>
+        <v>3.863924114042146</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.221033150050667</v>
+        <v>-5.182142701633056</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7868144022314705</v>
+        <v>0.8023705815985145</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6768938554613367</v>
+        <v>-0.7322111724892252</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.469447773288683</v>
+        <v>2.43625738307195</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.737629461003941</v>
+        <v>3.457610748596841</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.631832191941115</v>
+        <v>2.635702254701812</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.221033150050667</v>
+        <v>-5.182142701633056</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7868144022314705</v>
+        <v>0.8023705815985145</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.6768938554613367</v>
+        <v>-0.7322111724892252</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.624895988927483</v>
+        <v>2.62876605168818</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-24.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>452.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.8%</t>
+          <t>-686.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>466.1%</t>
+          <t>-161.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-296.0%</t>
+          <t>-298.6%</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.9%</t>
+          <t>-157.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-297.2%</t>
+          <t>-297.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.1%</t>
+          <t>-202.8%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729894</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440637</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608603</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390588</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297402</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158925</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940723</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646222</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.77881529651684</v>
+        <v>-10.83867206281974</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.12936543408754</v>
+        <v>-1.153308140608702</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.814861637417943</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.493600126382178</v>
+        <v>1.453495199919101</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611573</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.49490656558809</v>
+        <v>-10.554763331891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.010068237477403</v>
+        <v>-1.034010943998566</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.814861637417943</v>
+        <v>-2.881703181523071</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.499333830620814</v>
+        <v>1.459228904157738</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.42354017297844</v>
+        <v>-10.48339693928135</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9912589428274101</v>
+        <v>-1.015201649348572</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.743495244808295</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.532416403792738</v>
+        <v>1.492311477329662</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.15970330577437</v>
+        <v>-10.21956007207728</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8956076772586896</v>
+        <v>-0.919550383779852</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.743495244808295</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.52253292247983</v>
+        <v>1.482427996016754</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.892461504905976</v>
+        <v>-9.952318271208881</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7905455174107043</v>
+        <v>-0.8144882239318663</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.743495244808295</v>
+        <v>-2.810336788913423</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.520698361980457</v>
+        <v>1.48059343551738</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311951</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.794554466229485</v>
+        <v>-9.85441123253239</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7516830169135686</v>
+        <v>-0.775625723434731</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.675509494947739</v>
+        <v>-2.742351039052866</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.56118949692333</v>
+        <v>1.521084570460253</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.770600925253527</v>
+        <v>-9.830457691556433</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7414330943776921</v>
+        <v>-0.765375800898854</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.651555953971781</v>
+        <v>-2.718397498076909</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.576230127654398</v>
+        <v>1.536125201191321</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.50654098693073</v>
+        <v>-9.566397753233636</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6490694352103255</v>
+        <v>-0.6730121417314878</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.387496015648985</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.721405774486323</v>
+        <v>1.681300848023247</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.799461363425893</v>
+        <v>-8.859318129728798</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3690246194686915</v>
+        <v>-0.3929673259898534</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.387496015648985</v>
+        <v>-2.454337559754113</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.718618740826022</v>
+        <v>1.678513814362946</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.759277065059702</v>
+        <v>-8.819133831362608</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3526072762343739</v>
+        <v>-0.3765499827555359</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.347311717282794</v>
+        <v>-2.414153261387922</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.743072943733578</v>
+        <v>1.702968017270502</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.679207269521898</v>
+        <v>-8.739064035824804</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.321212536798495</v>
+        <v>-0.3451552433196574</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.26724192174499</v>
+        <v>-2.334083465850118</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.790481642277018</v>
+        <v>1.750376715813941</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291816</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.4457260472923</v>
+        <v>-8.505582813595204</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2198956190688035</v>
+        <v>-0.243838325589965</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.033760699515392</v>
+        <v>-2.100602243620519</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.938494804452629</v>
+        <v>1.898389877989553</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.296059656284786</v>
+        <v>-8.35591642258769</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1629212729787572</v>
+        <v>-0.1868639794999187</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.940857208272856</v>
+        <v>-2.007698752377983</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.991344688885191</v>
+        <v>1.951239762422115</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.163784182653899</v>
+        <v>-8.223640948956803</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1146435967793753</v>
+        <v>-0.1385863033005368</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.808581734641969</v>
+        <v>-1.875423278747097</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.06607745981075</v>
+        <v>2.025972533347674</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105958</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.973184507980746</v>
+        <v>-8.033041274283649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.03558866622247736</v>
+        <v>-0.0595313727436384</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.617982059968816</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.183252325302279</v>
+        <v>2.143147398839202</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.724184709297165</v>
+        <v>-7.784041475600068</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07691759447461388</v>
+        <v>0.0529748879534524</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.617982059968816</v>
+        <v>-1.684823604073944</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.196158666525938</v>
+        <v>2.156053740062861</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.82977469907027</v>
+        <v>-7.889631465373173</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.09329433103384677</v>
+        <v>-0.1172370375550078</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.723572049741921</v>
+        <v>-1.790413593847048</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.004828743062856</v>
+        <v>1.96472381659978</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987909</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.848509601188867</v>
+        <v>-7.908366367491769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05224395000419912</v>
+        <v>-0.07618665652536016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.729168059402052</v>
+        <v>-1.79600960350718</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.050015479143864</v>
+        <v>2.009910552680787</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.700569559781267</v>
+        <v>-7.76042632608417</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.112946856129327</v>
+        <v>-0.136889562650488</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.708847143493494</v>
+        <v>-1.775688687598622</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.942329106000831</v>
+        <v>1.902224179537755</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409212</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.683411409649973</v>
+        <v>-7.743268175952876</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1147975823302874</v>
+        <v>-0.1387402888514488</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.6916889933622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.943910009826129</v>
+        <v>1.903805083363053</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098116</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.639863002879283</v>
+        <v>-7.699719769182185</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1043388317171043</v>
+        <v>-0.1282815382382658</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.6916889933622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.936949397731036</v>
+        <v>1.89684447126796</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.397714609425424</v>
+        <v>-7.457571375728327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.006982880045582007</v>
+        <v>-0.01695982647557948</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.6916889933622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.951411752112179</v>
+        <v>1.911306825649103</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722823</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.289455472302903</v>
+        <v>-7.349312238605806</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04481865535378571</v>
+        <v>0.02087594883262422</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.6916889933622</v>
+        <v>-1.758530537467328</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.945943872571374</v>
+        <v>1.905838946108298</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792053</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.166164337485772</v>
+        <v>-7.226021103788675</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.09163320329121483</v>
+        <v>0.06769049677005379</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.56839785854507</v>
+        <v>-1.635239402650197</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.017416647472229</v>
+        <v>1.977311721009153</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919914</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.145015138582329</v>
+        <v>-7.204871904885231</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1077938610899172</v>
+        <v>0.08385115456875614</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.547248659641626</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.03780714505162</v>
+        <v>1.997702218588544</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318099</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.901249696598884</v>
+        <v>-6.961106462901787</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2010807462303457</v>
+        <v>0.1771380397091846</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.547248659641626</v>
+        <v>-1.614090203746754</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.033587853398671</v>
+        <v>1.993482926935595</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057532</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.799486876321589</v>
+        <v>-6.859343642624492</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2439101882612795</v>
+        <v>0.2199674817401185</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.534029591249198</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.043643608354144</v>
+        <v>2.003538681891068</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279192</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.549636482372515</v>
+        <v>-6.609493248675418</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3365924208246116</v>
+        <v>0.3126497143034506</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.534029591249198</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.036385683337847</v>
+        <v>1.99628075687477</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011505</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.373744389905083</v>
+        <v>-6.433601156207985</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4105483813322333</v>
+        <v>0.3866056748110722</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.534029591249198</v>
+        <v>-1.600871135354325</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.039984806858495</v>
+        <v>1.999879880395419</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392994</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.202297926882619</v>
+        <v>-6.262154693185521</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4924544725957722</v>
+        <v>0.4685117660746116</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.362583128226734</v>
+        <v>-1.429424672331862</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.156180190726527</v>
+        <v>2.116075264263451</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632789</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.194752954940125</v>
+        <v>-6.248676573980624</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4944929389890671</v>
+        <v>0.4729234913728675</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.35503815628424</v>
+        <v>-1.415946553126964</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.15972765150832</v>
+        <v>2.123182613402686</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.13111721270619</v>
+        <v>-6.185040831746689</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.524642036936958</v>
+        <v>0.5030725893207584</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.291402414050305</v>
+        <v>-1.35231081089303</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.202603897902999</v>
+        <v>2.166058859797364</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.038117171500292</v>
+        <v>-6.092040790540791</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.543036312203113</v>
+        <v>0.5214668645869134</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.291402414050305</v>
+        <v>-1.35231081089303</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.183798156686795</v>
+        <v>2.14725311858116</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242299</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.797686674695432</v>
+        <v>-5.851610293735931</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6409515875499348</v>
+        <v>0.6193821399337351</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.050971917245445</v>
+        <v>-1.111880314088169</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.329799531394588</v>
+        <v>2.293254493288953</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367689</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.725444106524237</v>
+        <v>-5.779367725564736</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6737779286532328</v>
+        <v>0.6522084810370332</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.050971917245445</v>
+        <v>-1.111880314088169</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.333728845229408</v>
+        <v>2.297183807123774</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.672445784242849</v>
+        <v>-5.726369403283348</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.695655841483128</v>
+        <v>0.6740863938669284</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9956356582435062</v>
+        <v>-1.05654405508623</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.367609184547911</v>
+        <v>2.331064146442277</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.563640898763122</v>
+        <v>-5.617564517803621</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.736175866895012</v>
+        <v>0.7146064192788124</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9956356582435062</v>
+        <v>-1.05654405508623</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.364607255767905</v>
+        <v>2.328062217662271</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675944</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.343620100726111</v>
+        <v>-5.397543719766611</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8257632231204304</v>
+        <v>0.8041937755042308</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.854415813175526</v>
+        <v>-0.9153242100182502</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.450918199819307</v>
+        <v>2.414373161713673</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.210752411662834</v>
+        <v>-5.264676030703333</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8948044815475651</v>
+        <v>0.8732350339313655</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.854415813175526</v>
+        <v>-0.9153242100182502</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.46681238262113</v>
+        <v>2.430267344515496</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496268</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.051237308143464</v>
+        <v>-5.105160927183963</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9597563673956149</v>
+        <v>0.9381869197794153</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.694900709656156</v>
+        <v>-0.7558091064988802</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.563667289173054</v>
+        <v>2.52712225106742</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577005</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.906565163043727</v>
+        <v>-4.960488782084226</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.027713327996949</v>
+        <v>1.00614388038075</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5502285645564187</v>
+        <v>-0.6111369613991429</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.660558678794337</v>
+        <v>2.624013640688702</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.73583922294211</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.966439990401419</v>
+        <v>-5.020363609441918</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9898008884552985</v>
+        <v>0.9682314408390988</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6101033919141108</v>
+        <v>-0.671011788756835</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.610671273781147</v>
+        <v>2.574126235675513</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674522</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.879640492622411</v>
+        <v>-4.933564111662909</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.046921180889468</v>
+        <v>1.025351733273269</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6101033919141108</v>
+        <v>-0.671011788756835</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.633071767103713</v>
+        <v>2.596526728998079</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430701</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.882110199084217</v>
+        <v>-4.936033818124715</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.046005699678158</v>
+        <v>1.024436252061958</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.612573098375917</v>
+        <v>-0.6734814952186412</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.631662344600042</v>
+        <v>2.595117306494407</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003609</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.950480385408227</v>
+        <v>-5.004404004448725</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.029664547623256</v>
+        <v>1.008095100007056</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6032973993397021</v>
+        <v>-0.6642057961824263</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.648234686496473</v>
+        <v>2.611689648390838</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508378</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.059018566324361</v>
+        <v>-5.112942185364859</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9766859838886934</v>
+        <v>0.9551165362724938</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6032973993397021</v>
+        <v>-0.6642057961824263</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.638671395128364</v>
+        <v>2.602126357022729</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.090011725653066</v>
+        <v>-5.143935344693564</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7889982851975978</v>
+        <v>0.7674288375813987</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6032973993397021</v>
+        <v>-0.6642057961824263</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.463380960168751</v>
+        <v>2.426835922063116</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.914537465860597</v>
+        <v>-4.968461084901096</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8637552211063733</v>
+        <v>0.8421857734901739</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6032973993397021</v>
+        <v>-0.6642057961824263</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.467948192160538</v>
+        <v>2.431403154054904</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.025473718501846</v>
+        <v>-5.079397337542344</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7951227488110808</v>
+        <v>0.7735533011948816</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6032973993397021</v>
+        <v>-0.6642057961824263</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.443690220921745</v>
+        <v>2.407145182816111</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111302</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.228500296045079</v>
+        <v>-5.282423915085578</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7170435030136928</v>
+        <v>0.6954740553974936</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8063239768829354</v>
+        <v>-0.8672323737256596</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.325005659615711</v>
+        <v>2.288460621510077</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.070574697109786</v>
+        <v>-5.124498316150285</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7903861290199425</v>
+        <v>0.7688166814037434</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8063239768829354</v>
+        <v>-0.8672323737256596</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.335178046047843</v>
+        <v>2.298633007942209</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742307</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.984331234083409</v>
+        <v>-5.038254853123907</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8198297848043539</v>
+        <v>0.7982603371881547</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8063239768829354</v>
+        <v>-0.8672323737256596</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.330124316621704</v>
+        <v>2.293579278516069</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316054</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.029638053482389</v>
+        <v>-5.083561672522887</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7934828324892877</v>
+        <v>0.7719133848730881</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8471341398921662</v>
+        <v>-0.9080425367348904</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.297413994260691</v>
+        <v>2.260868956155056</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803199</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.05867115818469</v>
+        <v>-5.112594777225188</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7824214636414686</v>
+        <v>0.7608520160252694</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8471341398921662</v>
+        <v>-0.9080425367348904</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.297965867293792</v>
+        <v>2.261420829188158</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.96586067673383</v>
+        <v>-5.019784295774328</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7488183481131783</v>
+        <v>0.7272489004969791</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7543236584413069</v>
+        <v>-0.8152320552840311</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.282924848055674</v>
+        <v>2.246379809950039</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.010250146063258</v>
+        <v>-5.064173765103756</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.732936036306008</v>
+        <v>0.7113665886898088</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7987131277707346</v>
+        <v>-0.8596215246134588</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.258164642382618</v>
+        <v>2.221619604276984</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.897578927827007</v>
+        <v>-4.951502546867506</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.773080232112231</v>
+        <v>0.7515107844960318</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6860419095344843</v>
+        <v>-0.7469503063772085</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.320843081836091</v>
+        <v>2.284298043730457</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.785201926644334</v>
+        <v>-4.839125545684833</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8235223284159674</v>
+        <v>0.8019528807997682</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6860419095344843</v>
+        <v>-0.7469503063772085</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.326334377666758</v>
+        <v>2.289789339561124</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.983436495531065</v>
+        <v>-5.037360114571563</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7557257026298143</v>
+        <v>0.7341562550136151</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.8842764784212149</v>
+        <v>-0.9451848752639391</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.218890838103259</v>
+        <v>2.182345799997624</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.066437776556344</v>
+        <v>-5.120361395596842</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.560880910220356</v>
+        <v>0.5393114626041569</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.9028473629483886</v>
+        <v>-0.9637557597911128</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.046104027387608</v>
+        <v>2.009558989281974</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.175051854999675</v>
+        <v>-5.228975474040173</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6375849395622293</v>
+        <v>0.6160154919460297</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.9028473629483886</v>
+        <v>-0.9637557597911128</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.166253688106814</v>
+        <v>2.129708650001179</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190776</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.261650437980778</v>
+        <v>-5.283539699635039</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6174585324721109</v>
+        <v>0.6087028278104065</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.9028473629483886</v>
+        <v>-0.9637557597911128</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.180766714209136</v>
+        <v>2.144221676103502</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.223266775422627</v>
+        <v>-5.245156037076888</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6302314388377401</v>
+        <v>0.6214757341760357</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.8644637003902375</v>
+        <v>-0.9253720972329617</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.201216353086396</v>
+        <v>2.164671314980762</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532491</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.046150445387461</v>
+        <v>-5.068039707041722</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6978069996971086</v>
+        <v>0.6890512950354042</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.8644637003902375</v>
+        <v>-0.9253720972329617</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.197945381931698</v>
+        <v>2.161400343826064</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793908</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.016448321411167</v>
+        <v>-5.038337583065428</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7103712410495389</v>
+        <v>0.7016155363878345</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.8689338256055508</v>
+        <v>-0.929842222448275</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.195946698564423</v>
+        <v>2.159401660458789</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011241</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.8370729001724</v>
+        <v>-4.858962161826661</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7759083848514603</v>
+        <v>0.7671526801897561</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.7121570674348321</v>
+        <v>-0.7730654642775563</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.283799728773269</v>
+        <v>2.247254690667634</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.882087113693006</v>
+        <v>-4.903976375347266</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7387101547748078</v>
+        <v>0.7299544501131034</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.7425059627494367</v>
+        <v>-0.8034143595921609</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.246397846916095</v>
+        <v>2.209852808810461</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.149091623965441</v>
+        <v>-5.170980885619701</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6375999130047796</v>
+        <v>0.6288442083430752</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.9368690007923852</v>
+        <v>-0.9977773976351094</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.135471586429272</v>
+        <v>2.098926548323638</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.250289405402613</v>
+        <v>-5.272178667056874</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5963247223264121</v>
+        <v>0.5875690176647077</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.005277814337704</v>
+        <v>-1.066186211180429</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.093630220198582</v>
+        <v>2.057085182092948</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815463</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.217813819231841</v>
+        <v>-5.239703080886102</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6069149183490374</v>
+        <v>0.598159213687333</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.005277814337704</v>
+        <v>-1.066186211180429</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.091230181752899</v>
+        <v>2.054685143647264</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.198775691524544</v>
+        <v>-5.220664953178805</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6110548886402012</v>
+        <v>0.6022991839784972</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.063461425668899</v>
+        <v>-1.124369822511623</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.052844734162427</v>
+        <v>2.016299696056793</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131258</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.229902322675162</v>
+        <v>-5.251791584329423</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7761861051186347</v>
+        <v>0.7674304004569303</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.063461425668899</v>
+        <v>-1.124369822511623</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.230426603101108</v>
+        <v>2.193881564995473</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.282222703275954</v>
+        <v>-5.304111964930215</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7560912818644514</v>
+        <v>0.747335577202747</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.028514565660027</v>
+        <v>-1.089422962502751</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.252228048092564</v>
+        <v>2.21568300998693</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078913</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.302480001804912</v>
+        <v>-5.324369263459173</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.753996892849794</v>
+        <v>0.74524118818809</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.028514565660027</v>
+        <v>-1.089422962502751</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.25823657848949</v>
+        <v>2.221691540383856</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.154737031569909</v>
+        <v>-5.17662629322417</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8922467287358171</v>
+        <v>0.8834910240741127</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.8607072084251436</v>
+        <v>-0.9216156052678678</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.438073640622442</v>
+        <v>2.401528602516808</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.256751714101131</v>
+        <v>-5.278640975755391</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8542344772548094</v>
+        <v>0.8454787725931054</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.8607072084251436</v>
+        <v>-0.9216156052678678</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.440867262153923</v>
+        <v>2.404322224048289</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394736</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.120142370007038</v>
+        <v>-5.142031631661299</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9095405632841049</v>
+        <v>0.9007848586224005</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.7240978643310512</v>
+        <v>-0.7850062611737754</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.523495217002037</v>
+        <v>2.486950178896403</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.262907702829688</v>
+        <v>-5.284796964483949</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8515149068951553</v>
+        <v>0.8427592022334509</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.8668631971537015</v>
+        <v>-0.9277715939964257</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.436916494048557</v>
+        <v>2.400371455942923</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.200609704053566</v>
+        <v>-5.222498965707826</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9427696602024249</v>
+        <v>0.9340139555407205</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.8668631971537015</v>
+        <v>-0.9277715939964257</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.503252047845378</v>
+        <v>2.466707009739744</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.998819506388408</v>
+        <v>-5.020708768042669</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7320666116578862</v>
+        <v>0.7233109069961818</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.6688450049845471</v>
+        <v>-0.7297534018272713</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.330643835536268</v>
+        <v>2.294098797430634</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.938928824745815</v>
+        <v>-4.960818086400075</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8263131166370987</v>
+        <v>0.8175574119753946</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6089543233419537</v>
+        <v>-0.6698627201846779</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.436868476844</v>
+        <v>2.400323438738365</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.036669369370789</v>
+        <v>-5.05855863102505</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8018446349031527</v>
+        <v>0.7930889302414483</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6248436014749339</v>
+        <v>-0.6857519983176581</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.441962646080255</v>
+        <v>2.405417607974621</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248939</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.213007129493718</v>
+        <v>-5.234896391147979</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7298455116786524</v>
+        <v>0.7210898070169485</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8011813615978634</v>
+        <v>-0.8620897584405876</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.334695970831169</v>
+        <v>2.298150932725535</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.8364116723978</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.212317757332495</v>
+        <v>-5.234207018986756</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7286128785830703</v>
+        <v>0.7198571739213659</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8011813615978634</v>
+        <v>-0.8620897584405876</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.333187588871098</v>
+        <v>2.296642550765464</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024968</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.218888722387088</v>
+        <v>-5.240777984041348</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7258473599966697</v>
+        <v>0.7170916553349653</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8077523266524562</v>
+        <v>-0.8686607234951804</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.329107877273779</v>
+        <v>2.292562839168144</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863231</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.210934752092315</v>
+        <v>-5.232824013746576</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7290289481145784</v>
+        <v>0.720273243452874</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8077523266524562</v>
+        <v>-0.8686607234951804</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.329107877273779</v>
+        <v>2.292562839168144</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83304018194759</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.200561375759229</v>
+        <v>-5.222450637413489</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7395600556756179</v>
+        <v>0.7308043510139135</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7973789503193689</v>
+        <v>-0.8582873471620931</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.341713660101435</v>
+        <v>2.305168621995801</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326883</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.072877065964932</v>
+        <v>-5.094766327619193</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7955261529680611</v>
+        <v>0.7867704483063567</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.6696946405250724</v>
+        <v>-0.7306030373677966</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.423216619352738</v>
+        <v>2.386671581247104</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314558</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.133543656367321</v>
+        <v>-5.155432918021582</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7580141892829779</v>
+        <v>0.7492584846212735</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.7513929572436061</v>
+        <v>-0.8123013540863303</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.36095230179749</v>
+        <v>2.324407263691856</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690033</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.068549796433675</v>
+        <v>-5.090439058087936</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7881094358670646</v>
+        <v>0.7793537312053602</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7245623426394507</v>
+        <v>-0.7854707394821749</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.381148373170612</v>
+        <v>2.344603335064978</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674316</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.169308432190673</v>
+        <v>-5.191197693844934</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7519669211953435</v>
+        <v>0.7432112165336391</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.8133879113664562</v>
+        <v>-0.8742963082091804</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.332013971565487</v>
+        <v>2.295468933459852</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163225</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.125105595104773</v>
+        <v>-5.146994856759034</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7755276585575408</v>
+        <v>0.7667719538958364</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.7691850742805557</v>
+        <v>-0.8300934711232799</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.364415276344864</v>
+        <v>2.32787023823923</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83822866302291</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.162084622768216</v>
+        <v>-5.183973884422477</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7591460479614112</v>
+        <v>0.7503903432997068</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.7322111724892252</v>
+        <v>-0.7931195693319494</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.38500961788891</v>
+        <v>2.348464579783275</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042146</v>
+        <v>3.86392411404214</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.182142701633056</v>
+        <v>-5.204031963287317</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8023705815985145</v>
+        <v>0.7936148769368105</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.7322111724892252</v>
+        <v>-0.7931195693319494</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.43625738307195</v>
+        <v>2.399712344966315</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.457610748596841</v>
+        <v>3.753510059045479</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.635702254701812</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.182142701633056</v>
+        <v>-5.243897610757781</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8023705815985145</v>
+        <v>0.7761093225428781</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7322111724892252</v>
+        <v>-0.7367692061540011</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.62876605168818</v>
+        <v>2.431963267467337</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240605.xlsx
+++ b/tame_output/ON/bt/strategyON_20240605.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.5%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.0%</t>
+          <t>-664.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.6%</t>
+          <t>-290.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-297.7%</t>
+          <t>-282.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.8%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.248676573980624</v>
+        <v>-6.037121693516698</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4729234913728675</v>
+        <v>0.5575454435584377</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.415946553126964</v>
+        <v>-1.204391672663039</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.123182613402686</v>
+        <v>2.250115541681041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.185040831746689</v>
+        <v>-5.973485951282764</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5030725893207584</v>
+        <v>0.5876945415063286</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.35231081089303</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.166058859797364</v>
+        <v>2.292991788075719</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.092040790540791</v>
+        <v>-5.880485910076866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5214668645869134</v>
+        <v>0.6060888167724836</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.35231081089303</v>
+        <v>-1.140755930429105</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.14725311858116</v>
+        <v>2.274186046859515</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.851610293735931</v>
+        <v>-5.640055413272005</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6193821399337351</v>
+        <v>0.7040040921193054</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.111880314088169</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.293254493288953</v>
+        <v>2.420187421567308</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.779367725564736</v>
+        <v>-5.567812845100811</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6522084810370332</v>
+        <v>0.7368304332226034</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.111880314088169</v>
+        <v>-0.9003254336242443</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.297183807123774</v>
+        <v>2.424116735402129</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.726369403283348</v>
+        <v>-5.514814522819423</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6740863938669284</v>
+        <v>0.7587083460524986</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.05654405508623</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.331064146442277</v>
+        <v>2.457997074720632</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.617564517803621</v>
+        <v>-5.406009637339696</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7146064192788124</v>
+        <v>0.7992283714643826</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.05654405508623</v>
+        <v>-0.8449891746223055</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.328062217662271</v>
+        <v>2.454995145940625</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.397543719766611</v>
+        <v>-5.185988839302685</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8041937755042308</v>
+        <v>0.888815727689801</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9153242100182502</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.414373161713673</v>
+        <v>2.541306089992028</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.264676030703333</v>
+        <v>-5.053121150239408</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8732350339313655</v>
+        <v>0.9578569861169353</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9153242100182502</v>
+        <v>-0.7037693295543253</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.430267344515496</v>
+        <v>2.557200272793851</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.105160927183963</v>
+        <v>-4.893606046720038</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9381869197794153</v>
+        <v>1.022808871964985</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7558091064988802</v>
+        <v>-0.5442542260349553</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.52712225106742</v>
+        <v>2.654055179345775</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.960488782084226</v>
+        <v>-4.7489339016203</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.00614388038075</v>
+        <v>1.09076583256632</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6111369613991429</v>
+        <v>-0.3995820809352179</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.624013640688702</v>
+        <v>2.750946568967057</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.020363609441918</v>
+        <v>-4.808808728977993</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9682314408390988</v>
+        <v>1.052853393024669</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.671011788756835</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.574126235675513</v>
+        <v>2.701059163953868</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.933564111662909</v>
+        <v>-4.722009231198983</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.025351733273269</v>
+        <v>1.109973685458839</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.671011788756835</v>
+        <v>-0.45945690829291</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.596526728998079</v>
+        <v>2.723459657276434</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.936033818124715</v>
+        <v>-4.724478937660789</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.024436252061958</v>
+        <v>1.109058204247529</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6734814952186412</v>
+        <v>-0.4619266147547162</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.595117306494407</v>
+        <v>2.722050234772762</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.004404004448725</v>
+        <v>-4.7928491239848</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.008095100007056</v>
+        <v>1.092717052192626</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6642057961824263</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.611689648390838</v>
+        <v>2.738622576669193</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.112942185364859</v>
+        <v>-4.901387304900934</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9551165362724938</v>
+        <v>1.039738488458064</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6642057961824263</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.602126357022729</v>
+        <v>2.729059285301084</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.143935344693564</v>
+        <v>-4.932380464229639</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7674288375813987</v>
+        <v>0.8520507897669689</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6642057961824263</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.426835922063116</v>
+        <v>2.553768850341471</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.968461084901096</v>
+        <v>-4.75690620443717</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8421857734901739</v>
+        <v>0.9268077256757441</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6642057961824263</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.431403154054904</v>
+        <v>2.558336082333259</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.079397337542344</v>
+        <v>-4.867842457078419</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7735533011948816</v>
+        <v>0.8581752533804516</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6642057961824263</v>
+        <v>-0.4526509157185012</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.407145182816111</v>
+        <v>2.534078111094466</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.282423915085578</v>
+        <v>-5.070869034621652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6954740553974936</v>
+        <v>0.7800960075830639</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8672323737256596</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.288460621510077</v>
+        <v>2.415393549788432</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.124498316150285</v>
+        <v>-4.912943435686359</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7688166814037434</v>
+        <v>0.8534386335893134</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8672323737256596</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.298633007942209</v>
+        <v>2.425565936220564</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.038254853123907</v>
+        <v>-4.826699972659982</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7982603371881547</v>
+        <v>0.8828822893737249</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8672323737256596</v>
+        <v>-0.6556774932617346</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.293579278516069</v>
+        <v>2.420512206794424</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.083561672522887</v>
+        <v>-4.872006792058961</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7719133848730881</v>
+        <v>0.8565353370586584</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9080425367348904</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.260868956155056</v>
+        <v>2.387801884433411</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.112594777225188</v>
+        <v>-4.901039896761263</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7608520160252694</v>
+        <v>0.8454739682108396</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9080425367348904</v>
+        <v>-0.6964876562709654</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.261420829188158</v>
+        <v>2.388353757466513</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.019784295774328</v>
+        <v>-4.808229415310403</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7272489004969791</v>
+        <v>0.8118708526825491</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8152320552840311</v>
+        <v>-0.6036771748201061</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.246379809950039</v>
+        <v>2.373312738228394</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.064173765103756</v>
+        <v>-4.85261888463983</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7113665886898088</v>
+        <v>0.7959885408753788</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8596215246134588</v>
+        <v>-0.6480666441495337</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.221619604276984</v>
+        <v>2.348552532555338</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.951502546867506</v>
+        <v>-4.73994766640358</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7515107844960318</v>
+        <v>0.836132736681602</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7469503063772085</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.284298043730457</v>
+        <v>2.411230972008811</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.839125545684833</v>
+        <v>-4.627570665220907</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8019528807997682</v>
+        <v>0.8865748329853385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.7469503063772085</v>
+        <v>-0.5353954259132836</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.289789339561124</v>
+        <v>2.416722267839479</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.037360114571563</v>
+        <v>-4.825805234107638</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.7341562550136151</v>
+        <v>0.8187782071991851</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.9451848752639391</v>
+        <v>-0.7336299948000142</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.182345799997624</v>
+        <v>2.309278728275979</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.120361395596842</v>
+        <v>-4.908806515132917</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.5393114626041569</v>
+        <v>0.6239334147897269</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.9637557597911128</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.009558989281974</v>
+        <v>2.136491917560329</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.228975474040173</v>
+        <v>-5.017420593576248</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.6160154919460297</v>
+        <v>0.7006374441315999</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.9637557597911128</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.129708650001179</v>
+        <v>2.256641578279534</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.283539699635039</v>
+        <v>-5.067200712048272</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6087028278104065</v>
+        <v>0.6952384228451134</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.9637557597911128</v>
+        <v>-0.7522008793271879</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.144221676103502</v>
+        <v>2.271154604381857</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.245156037076888</v>
+        <v>-5.028817049490121</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.6214757341760357</v>
+        <v>0.7080113292107422</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.9253720972329617</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.164671314980762</v>
+        <v>2.291604243259116</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.068039707041722</v>
+        <v>-4.851700719454955</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6890512950354042</v>
+        <v>0.7755868900701106</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.9253720972329617</v>
+        <v>-0.7138172167690368</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.161400343826064</v>
+        <v>2.288333272104418</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.038337583065428</v>
+        <v>-4.821998595478662</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7016155363878345</v>
+        <v>0.7881511314225413</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.929842222448275</v>
+        <v>-0.7182873419843501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.159401660458789</v>
+        <v>2.286334588737144</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.858962161826661</v>
+        <v>-4.642623174239894</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.7671526801897561</v>
+        <v>0.8536882752244628</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.7730654642775563</v>
+        <v>-0.5615105838136314</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.247254690667634</v>
+        <v>2.374187618945989</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.903976375347266</v>
+        <v>-4.6876373877605</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7299544501131034</v>
+        <v>0.8164900451478101</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.8034143595921609</v>
+        <v>-0.591859479128236</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.209852808810461</v>
+        <v>2.336785737088816</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.170980885619701</v>
+        <v>-4.954641898032935</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6288442083430752</v>
+        <v>0.7153798033777818</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.9977773976351094</v>
+        <v>-0.7862225171711845</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.098926548323638</v>
+        <v>2.225859476601993</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.272178667056874</v>
+        <v>-5.055839679470107</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.5875690176647077</v>
+        <v>0.6741046126994141</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.066186211180429</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.057085182092948</v>
+        <v>2.184018110371303</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.239703080886102</v>
+        <v>-5.023364093299335</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.598159213687333</v>
+        <v>0.6846948087220399</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.066186211180429</v>
+        <v>-0.8546313307165037</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.054685143647264</v>
+        <v>2.18161807192562</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.220664953178805</v>
+        <v>-5.004325965592038</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6022991839784972</v>
+        <v>0.6888347790132037</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.124369822511623</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.016299696056793</v>
+        <v>2.143232624335147</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.251791584329423</v>
+        <v>-5.035452596742656</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.7674304004569303</v>
+        <v>0.8539659954916368</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.124369822511623</v>
+        <v>-0.9128149420476982</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.193881564995473</v>
+        <v>2.320814493273828</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.304111964930215</v>
+        <v>-5.087772977343448</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.747335577202747</v>
+        <v>0.8338711722374539</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.089422962502751</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.21568300998693</v>
+        <v>2.342615938265285</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.324369263459173</v>
+        <v>-5.108030275872406</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.74524118818809</v>
+        <v>0.8317767832227965</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.089422962502751</v>
+        <v>-0.877868082038826</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.221691540383856</v>
+        <v>2.348624468662211</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.17662629322417</v>
+        <v>-4.960287305637403</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8834910240741127</v>
+        <v>0.9700266191088194</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9216156052678678</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.401528602516808</v>
+        <v>2.528461530795163</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.278640975755391</v>
+        <v>-5.062301988168625</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8454787725931054</v>
+        <v>0.9320143676278119</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9216156052678678</v>
+        <v>-0.7100607248039429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.404322224048289</v>
+        <v>2.531255152326644</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.142031631661299</v>
+        <v>-4.925692644074532</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9007848586224005</v>
+        <v>0.9873204536571074</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.7850062611737754</v>
+        <v>-0.5734513807098505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.486950178896403</v>
+        <v>2.613883107174757</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.284796964483949</v>
+        <v>-5.068457976897182</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8427592022334509</v>
+        <v>0.9292947972681573</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9277715939964257</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.400371455942923</v>
+        <v>2.527304384221277</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.222498965707826</v>
+        <v>-5.00615997812106</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9340139555407205</v>
+        <v>1.020549550575427</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9277715939964257</v>
+        <v>-0.7162167135325008</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.466707009739744</v>
+        <v>2.593639938018098</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.020708768042669</v>
+        <v>-4.804369780455902</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7233109069961818</v>
+        <v>0.8098465020308885</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7297534018272713</v>
+        <v>-0.5181985213633464</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.294098797430634</v>
+        <v>2.421031725708989</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.960818086400075</v>
+        <v>-4.744479098813309</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8175574119753946</v>
+        <v>0.904093007010101</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.6698627201846779</v>
+        <v>-0.458307839720753</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.400323438738365</v>
+        <v>2.527256367016721</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.05855863102505</v>
+        <v>-4.842219643438283</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7930889302414483</v>
+        <v>0.879624525276155</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.6857519983176581</v>
+        <v>-0.4741971178537331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.405417607974621</v>
+        <v>2.532350536252976</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.234896391147979</v>
+        <v>-5.018557403561212</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7210898070169485</v>
+        <v>0.8076254020516549</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.8620897584405876</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.298150932725535</v>
+        <v>2.42508386100389</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.234207018986756</v>
+        <v>-5.017868031399989</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7198571739213659</v>
+        <v>0.8063927689560728</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.8620897584405876</v>
+        <v>-0.6505348779766625</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.296642550765464</v>
+        <v>2.423575479043818</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.240777984041348</v>
+        <v>-5.024438996454582</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7170916553349653</v>
+        <v>0.8036272503696718</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.8686607234951804</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.292562839168144</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.232824013746576</v>
+        <v>-5.01648502615981</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.720273243452874</v>
+        <v>0.8068088384875809</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.8686607234951804</v>
+        <v>-0.6571058430312555</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.292562839168144</v>
+        <v>2.419495767446499</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.222450637413489</v>
+        <v>-5.006111649826723</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7308043510139135</v>
+        <v>0.8173399460486201</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.8582873471620931</v>
+        <v>-0.6467324666981682</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.305168621995801</v>
+        <v>2.432101550274156</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.094766327619193</v>
+        <v>-4.878427340032427</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7867704483063567</v>
+        <v>0.8733060433410635</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7306030373677966</v>
+        <v>-0.5190481569038717</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.386671581247104</v>
+        <v>2.513604509525459</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.155432918021582</v>
+        <v>-4.939093930434815</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7492584846212735</v>
+        <v>0.8357940796559802</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.8123013540863303</v>
+        <v>-0.6007464736224054</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.324407263691856</v>
+        <v>2.451340191970211</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.090439058087936</v>
+        <v>-4.87410007050117</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7793537312053602</v>
+        <v>0.8658893262400671</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.7854707394821749</v>
+        <v>-0.57391585901825</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.344603335064978</v>
+        <v>2.471536263343332</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.191197693844934</v>
+        <v>-4.974858706258168</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7432112165336391</v>
+        <v>0.8297468115683457</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.8742963082091804</v>
+        <v>-0.6627414277452555</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.295468933459852</v>
+        <v>2.422401861738207</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.146994856759034</v>
+        <v>-4.930655869172267</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7667719538958364</v>
+        <v>0.8533075489305431</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8300934711232799</v>
+        <v>-0.618538590659355</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.32787023823923</v>
+        <v>2.454803166517585</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.183973884422477</v>
+        <v>-4.96763489683571</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7503903432997068</v>
+        <v>0.8369259383344136</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.7931195693319494</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.348464579783275</v>
+        <v>2.475397508061631</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86392411404214</v>
+        <v>3.863924114042142</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.204031963287317</v>
+        <v>-4.987692975700551</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7936148769368105</v>
+        <v>0.880150471971517</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.7931195693319494</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.399712344966315</v>
+        <v>2.52664527324467</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.753510059045479</v>
+        <v>3.753510059045481</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.243897610757781</v>
+        <v>-5.027498860176253</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7761093225428781</v>
+        <v>0.8626688227754888</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.7367692061540011</v>
+        <v>-0.5815646888680245</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.431963267467337</v>
+        <v>2.525085977838923</v>
       </c>
     </row>
   </sheetData>
